--- a/2026クラス検索データ.xlsx
+++ b/2026クラス検索データ.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\平　俊一\Desktop\たいら\2026総務\入学式\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\平　俊一\Desktop\たいら\2026総務\入学式\class-search\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D4E797B9-4598-4ACE-BD3A-6F80B2AA9405}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99D4C053-CF78-44B2-8FED-3A7BA566E268}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-12630" windowWidth="29040" windowHeight="15720" xr2:uid="{758807D2-BD72-4C96-989D-3C5BC57FB7BF}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{758807D2-BD72-4C96-989D-3C5BC57FB7BF}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3832" uniqueCount="1847">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3833" uniqueCount="1848">
   <si>
     <t>秋葉</t>
   </si>
@@ -5593,12 +5593,20 @@
   <si>
     <t>1872</t>
   </si>
+  <si>
+    <t>生年月日</t>
+    <phoneticPr fontId="2"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <numFmts count="2">
+    <numFmt numFmtId="176" formatCode="[$-411]ggge&quot;年&quot;mm&quot;月&quot;dd&quot;日&quot;;@"/>
+    <numFmt numFmtId="178" formatCode="yyyymmdd"/>
+  </numFmts>
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -5613,6 +5621,18 @@
       <family val="2"/>
       <charset val="128"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
     </font>
   </fonts>
   <fills count="2">
@@ -5637,8 +5657,17 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -5975,15 +6004,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0C68875-8201-4F1D-A118-AF4099536867}">
-  <dimension ref="A1:H479"/>
+  <dimension ref="A1:J479"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="11.3984375" customWidth="1"/>
-    <col min="4" max="7" width="10.69921875" customWidth="1"/>
-    <col min="8" max="8" width="27.59765625" bestFit="1" customWidth="1"/>
+    <col min="4" max="8" width="10.69921875" customWidth="1"/>
+    <col min="9" max="9" width="27.59765625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.3984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>1314</v>
       </c>
@@ -6005,11 +6035,14 @@
       <c r="G1" t="s">
         <v>1312</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
+        <v>1847</v>
+      </c>
+      <c r="I1" t="s">
         <v>1313</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>1317</v>
       </c>
@@ -6031,11 +6064,15 @@
       <c r="G2" t="s">
         <v>2</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="2">
+        <v>40287</v>
+      </c>
+      <c r="I2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="J2" s="3"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>1320</v>
       </c>
@@ -6057,11 +6094,14 @@
       <c r="G3" t="s">
         <v>6</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H3" s="2">
+        <v>40632</v>
+      </c>
+      <c r="I3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>1322</v>
       </c>
@@ -6083,11 +6123,14 @@
       <c r="G4" t="s">
         <v>10</v>
       </c>
-      <c r="H4" t="s">
+      <c r="H4" s="2">
+        <v>40491</v>
+      </c>
+      <c r="I4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>1324</v>
       </c>
@@ -6109,11 +6152,14 @@
       <c r="G5" t="s">
         <v>14</v>
       </c>
-      <c r="H5" t="s">
+      <c r="H5" s="2">
+        <v>40282</v>
+      </c>
+      <c r="I5" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>1326</v>
       </c>
@@ -6135,11 +6181,14 @@
       <c r="G6" t="s">
         <v>18</v>
       </c>
-      <c r="H6" t="s">
+      <c r="H6" s="2">
+        <v>40632</v>
+      </c>
+      <c r="I6" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>1328</v>
       </c>
@@ -6161,11 +6210,14 @@
       <c r="G7" t="s">
         <v>22</v>
       </c>
-      <c r="H7" t="s">
+      <c r="H7" s="2">
+        <v>40409</v>
+      </c>
+      <c r="I7" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>1330</v>
       </c>
@@ -6187,11 +6239,14 @@
       <c r="G8" t="s">
         <v>27</v>
       </c>
-      <c r="H8" t="s">
+      <c r="H8" s="2">
+        <v>40494</v>
+      </c>
+      <c r="I8" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>1332</v>
       </c>
@@ -6213,11 +6268,14 @@
       <c r="G9" t="s">
         <v>31</v>
       </c>
-      <c r="H9" t="s">
+      <c r="H9" s="2">
+        <v>40575</v>
+      </c>
+      <c r="I9" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>1334</v>
       </c>
@@ -6239,11 +6297,14 @@
       <c r="G10" t="s">
         <v>34</v>
       </c>
-      <c r="H10" t="s">
+      <c r="H10" s="2">
+        <v>40568</v>
+      </c>
+      <c r="I10" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>1336</v>
       </c>
@@ -6265,11 +6326,14 @@
       <c r="G11" t="s">
         <v>38</v>
       </c>
-      <c r="H11" t="s">
+      <c r="H11" s="2">
+        <v>40377</v>
+      </c>
+      <c r="I11" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>1338</v>
       </c>
@@ -6291,11 +6355,14 @@
       <c r="G12" t="s">
         <v>42</v>
       </c>
-      <c r="H12" t="s">
+      <c r="H12" s="2">
+        <v>40585</v>
+      </c>
+      <c r="I12" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>1340</v>
       </c>
@@ -6317,11 +6384,14 @@
       <c r="G13" t="s">
         <v>46</v>
       </c>
-      <c r="H13" t="s">
+      <c r="H13" s="2">
+        <v>40560</v>
+      </c>
+      <c r="I13" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>1342</v>
       </c>
@@ -6343,11 +6413,14 @@
       <c r="G14" t="s">
         <v>52</v>
       </c>
-      <c r="H14" t="s">
+      <c r="H14" s="2">
+        <v>40316</v>
+      </c>
+      <c r="I14" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>1344</v>
       </c>
@@ -6369,11 +6442,14 @@
       <c r="G15" t="s">
         <v>56</v>
       </c>
-      <c r="H15" t="s">
+      <c r="H15" s="2">
+        <v>40381</v>
+      </c>
+      <c r="I15" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>1346</v>
       </c>
@@ -6395,11 +6471,14 @@
       <c r="G16" t="s">
         <v>60</v>
       </c>
-      <c r="H16" t="s">
+      <c r="H16" s="2">
+        <v>40516</v>
+      </c>
+      <c r="I16" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>1348</v>
       </c>
@@ -6421,11 +6500,14 @@
       <c r="G17" t="s">
         <v>63</v>
       </c>
-      <c r="H17" t="s">
+      <c r="H17" s="2">
+        <v>40484</v>
+      </c>
+      <c r="I17" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>1350</v>
       </c>
@@ -6447,11 +6529,14 @@
       <c r="G18" t="s">
         <v>66</v>
       </c>
-      <c r="H18" t="s">
+      <c r="H18" s="2">
+        <v>40347</v>
+      </c>
+      <c r="I18" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>1352</v>
       </c>
@@ -6473,11 +6558,14 @@
       <c r="G19" t="s">
         <v>70</v>
       </c>
-      <c r="H19" t="s">
+      <c r="H19" s="2">
+        <v>40307</v>
+      </c>
+      <c r="I19" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>1354</v>
       </c>
@@ -6499,11 +6587,14 @@
       <c r="G20" t="s">
         <v>74</v>
       </c>
-      <c r="H20" t="s">
+      <c r="H20" s="2">
+        <v>40396</v>
+      </c>
+      <c r="I20" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>1356</v>
       </c>
@@ -6525,11 +6616,14 @@
       <c r="G21" t="s">
         <v>78</v>
       </c>
-      <c r="H21" t="s">
+      <c r="H21" s="2">
+        <v>40392</v>
+      </c>
+      <c r="I21" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>1358</v>
       </c>
@@ -6551,11 +6645,14 @@
       <c r="G22" t="s">
         <v>82</v>
       </c>
-      <c r="H22" t="s">
+      <c r="H22" s="2">
+        <v>40363</v>
+      </c>
+      <c r="I22" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>1360</v>
       </c>
@@ -6577,11 +6674,14 @@
       <c r="G23" t="s">
         <v>86</v>
       </c>
-      <c r="H23" t="s">
+      <c r="H23" s="2">
+        <v>40286</v>
+      </c>
+      <c r="I23" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>1362</v>
       </c>
@@ -6603,11 +6703,14 @@
       <c r="G24" t="s">
         <v>90</v>
       </c>
-      <c r="H24" t="s">
+      <c r="H24" s="2">
+        <v>40449</v>
+      </c>
+      <c r="I24" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>1364</v>
       </c>
@@ -6629,11 +6732,14 @@
       <c r="G25" t="s">
         <v>94</v>
       </c>
-      <c r="H25" t="s">
+      <c r="H25" s="2">
+        <v>40290</v>
+      </c>
+      <c r="I25" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>1366</v>
       </c>
@@ -6655,11 +6761,14 @@
       <c r="G26" t="s">
         <v>98</v>
       </c>
-      <c r="H26" t="s">
+      <c r="H26" s="2">
+        <v>40413</v>
+      </c>
+      <c r="I26" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>1368</v>
       </c>
@@ -6681,11 +6790,14 @@
       <c r="G27" t="s">
         <v>101</v>
       </c>
-      <c r="H27" t="s">
+      <c r="H27" s="2">
+        <v>40542</v>
+      </c>
+      <c r="I27" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>1370</v>
       </c>
@@ -6707,11 +6819,14 @@
       <c r="G28" t="s">
         <v>105</v>
       </c>
-      <c r="H28" t="s">
+      <c r="H28" s="2">
+        <v>40503</v>
+      </c>
+      <c r="I28" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>1372</v>
       </c>
@@ -6733,11 +6848,14 @@
       <c r="G29" t="s">
         <v>108</v>
       </c>
-      <c r="H29" t="s">
+      <c r="H29" s="2">
+        <v>40561</v>
+      </c>
+      <c r="I29" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>1374</v>
       </c>
@@ -6759,11 +6877,14 @@
       <c r="G30" t="s">
         <v>112</v>
       </c>
-      <c r="H30" t="s">
+      <c r="H30" s="2">
+        <v>40284</v>
+      </c>
+      <c r="I30" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>1376</v>
       </c>
@@ -6785,11 +6906,14 @@
       <c r="G31" t="s">
         <v>116</v>
       </c>
-      <c r="H31" t="s">
+      <c r="H31" s="2">
+        <v>40366</v>
+      </c>
+      <c r="I31" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>1378</v>
       </c>
@@ -6811,11 +6935,14 @@
       <c r="G32" t="s">
         <v>120</v>
       </c>
-      <c r="H32" t="s">
+      <c r="H32" s="2">
+        <v>40377</v>
+      </c>
+      <c r="I32" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>1380</v>
       </c>
@@ -6837,11 +6964,14 @@
       <c r="G33" t="s">
         <v>123</v>
       </c>
-      <c r="H33" t="s">
+      <c r="H33" s="2">
+        <v>40293</v>
+      </c>
+      <c r="I33" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>1381</v>
       </c>
@@ -6863,11 +6993,14 @@
       <c r="G34" t="s">
         <v>127</v>
       </c>
-      <c r="H34" t="s">
+      <c r="H34" s="2">
+        <v>40483</v>
+      </c>
+      <c r="I34" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
         <v>1382</v>
       </c>
@@ -6889,11 +7022,14 @@
       <c r="G35" t="s">
         <v>130</v>
       </c>
-      <c r="H35" t="s">
+      <c r="H35" s="2">
+        <v>40547</v>
+      </c>
+      <c r="I35" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
         <v>1383</v>
       </c>
@@ -6915,11 +7051,14 @@
       <c r="G36" t="s">
         <v>134</v>
       </c>
-      <c r="H36" t="s">
+      <c r="H36" s="2">
+        <v>40544</v>
+      </c>
+      <c r="I36" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
         <v>1384</v>
       </c>
@@ -6941,11 +7080,14 @@
       <c r="G37" t="s">
         <v>138</v>
       </c>
-      <c r="H37" t="s">
+      <c r="H37" s="2">
+        <v>40330</v>
+      </c>
+      <c r="I37" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
         <v>1385</v>
       </c>
@@ -6967,11 +7109,14 @@
       <c r="G38" t="s">
         <v>142</v>
       </c>
-      <c r="H38" t="s">
+      <c r="H38" s="2">
+        <v>40570</v>
+      </c>
+      <c r="I38" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
         <v>1386</v>
       </c>
@@ -6993,11 +7138,14 @@
       <c r="G39" t="s">
         <v>145</v>
       </c>
-      <c r="H39" t="s">
+      <c r="H39" s="2">
+        <v>40512</v>
+      </c>
+      <c r="I39" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
         <v>1387</v>
       </c>
@@ -7019,11 +7167,14 @@
       <c r="G40" t="s">
         <v>148</v>
       </c>
-      <c r="H40" t="s">
+      <c r="H40" s="2">
+        <v>40563</v>
+      </c>
+      <c r="I40" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
         <v>1388</v>
       </c>
@@ -7045,11 +7196,14 @@
       <c r="G41" t="s">
         <v>152</v>
       </c>
-      <c r="H41" t="s">
+      <c r="H41" s="2">
+        <v>40483</v>
+      </c>
+      <c r="I41" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
         <v>1389</v>
       </c>
@@ -7071,11 +7225,14 @@
       <c r="G42" t="s">
         <v>156</v>
       </c>
-      <c r="H42" t="s">
+      <c r="H42" s="2">
+        <v>40613</v>
+      </c>
+      <c r="I42" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
         <v>1390</v>
       </c>
@@ -7097,11 +7254,14 @@
       <c r="G43" t="s">
         <v>159</v>
       </c>
-      <c r="H43" t="s">
+      <c r="H43" s="2">
+        <v>40404</v>
+      </c>
+      <c r="I43" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
         <v>1391</v>
       </c>
@@ -7123,11 +7283,14 @@
       <c r="G44" t="s">
         <v>163</v>
       </c>
-      <c r="H44" t="s">
+      <c r="H44" s="2">
+        <v>40526</v>
+      </c>
+      <c r="I44" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
         <v>1392</v>
       </c>
@@ -7149,11 +7312,14 @@
       <c r="G45" t="s">
         <v>166</v>
       </c>
-      <c r="H45" t="s">
+      <c r="H45" s="2">
+        <v>40318</v>
+      </c>
+      <c r="I45" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
         <v>1393</v>
       </c>
@@ -7175,11 +7341,14 @@
       <c r="G46" t="s">
         <v>169</v>
       </c>
-      <c r="H46" t="s">
+      <c r="H46" s="2">
+        <v>40333</v>
+      </c>
+      <c r="I46" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
         <v>1394</v>
       </c>
@@ -7201,11 +7370,14 @@
       <c r="G47" t="s">
         <v>171</v>
       </c>
-      <c r="H47" t="s">
+      <c r="H47" s="2">
+        <v>40457</v>
+      </c>
+      <c r="I47" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
         <v>1395</v>
       </c>
@@ -7227,11 +7399,14 @@
       <c r="G48" t="s">
         <v>174</v>
       </c>
-      <c r="H48" t="s">
+      <c r="H48" s="2">
+        <v>40616</v>
+      </c>
+      <c r="I48" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
         <v>1396</v>
       </c>
@@ -7253,11 +7428,14 @@
       <c r="G49" t="s">
         <v>178</v>
       </c>
-      <c r="H49" t="s">
+      <c r="H49" s="2">
+        <v>40428</v>
+      </c>
+      <c r="I49" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
         <v>1397</v>
       </c>
@@ -7279,11 +7457,14 @@
       <c r="G50" t="s">
         <v>181</v>
       </c>
-      <c r="H50" t="s">
+      <c r="H50" s="2">
+        <v>40353</v>
+      </c>
+      <c r="I50" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
         <v>1398</v>
       </c>
@@ -7305,11 +7486,14 @@
       <c r="G51" t="s">
         <v>184</v>
       </c>
-      <c r="H51" t="s">
+      <c r="H51" s="2">
+        <v>40428</v>
+      </c>
+      <c r="I51" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
         <v>1399</v>
       </c>
@@ -7331,11 +7515,14 @@
       <c r="G52" t="s">
         <v>187</v>
       </c>
-      <c r="H52" t="s">
+      <c r="H52" s="2">
+        <v>40591</v>
+      </c>
+      <c r="I52" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
         <v>1400</v>
       </c>
@@ -7357,11 +7544,14 @@
       <c r="G53" t="s">
         <v>190</v>
       </c>
-      <c r="H53" t="s">
+      <c r="H53" s="2">
+        <v>40593</v>
+      </c>
+      <c r="I53" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
         <v>1401</v>
       </c>
@@ -7383,11 +7573,14 @@
       <c r="G54" t="s">
         <v>193</v>
       </c>
-      <c r="H54" t="s">
+      <c r="H54" s="2">
+        <v>40336</v>
+      </c>
+      <c r="I54" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
         <v>1402</v>
       </c>
@@ -7409,11 +7602,14 @@
       <c r="G55" t="s">
         <v>197</v>
       </c>
-      <c r="H55" t="s">
+      <c r="H55" s="2">
+        <v>40279</v>
+      </c>
+      <c r="I55" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
         <v>1403</v>
       </c>
@@ -7435,11 +7631,14 @@
       <c r="G56" t="s">
         <v>201</v>
       </c>
-      <c r="H56" t="s">
+      <c r="H56" s="2">
+        <v>40551</v>
+      </c>
+      <c r="I56" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
         <v>1404</v>
       </c>
@@ -7461,11 +7660,14 @@
       <c r="G57" t="s">
         <v>205</v>
       </c>
-      <c r="H57" t="s">
+      <c r="H57" s="2">
+        <v>40304</v>
+      </c>
+      <c r="I57" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
         <v>1405</v>
       </c>
@@ -7487,11 +7689,14 @@
       <c r="G58" t="s">
         <v>208</v>
       </c>
-      <c r="H58" t="s">
+      <c r="H58" s="2">
+        <v>40320</v>
+      </c>
+      <c r="I58" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
         <v>1406</v>
       </c>
@@ -7513,11 +7718,14 @@
       <c r="G59" t="s">
         <v>211</v>
       </c>
-      <c r="H59" t="s">
+      <c r="H59" s="2">
+        <v>40312</v>
+      </c>
+      <c r="I59" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A60" t="s">
         <v>1407</v>
       </c>
@@ -7539,11 +7747,14 @@
       <c r="G60" t="s">
         <v>214</v>
       </c>
-      <c r="H60" t="s">
+      <c r="H60" s="2">
+        <v>40410</v>
+      </c>
+      <c r="I60" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A61" t="s">
         <v>1408</v>
       </c>
@@ -7565,11 +7776,14 @@
       <c r="G61" t="s">
         <v>217</v>
       </c>
-      <c r="H61" t="s">
+      <c r="H61" s="2">
+        <v>40525</v>
+      </c>
+      <c r="I61" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A62" t="s">
         <v>1409</v>
       </c>
@@ -7591,11 +7805,14 @@
       <c r="G62" t="s">
         <v>219</v>
       </c>
-      <c r="H62" t="s">
+      <c r="H62" s="2">
+        <v>40365</v>
+      </c>
+      <c r="I62" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A63" t="s">
         <v>1411</v>
       </c>
@@ -7617,11 +7834,14 @@
       <c r="G63" t="s">
         <v>222</v>
       </c>
-      <c r="H63" t="s">
+      <c r="H63" s="2">
+        <v>40432</v>
+      </c>
+      <c r="I63" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A64" t="s">
         <v>1413</v>
       </c>
@@ -7643,11 +7863,14 @@
       <c r="G64" t="s">
         <v>226</v>
       </c>
-      <c r="H64" t="s">
+      <c r="H64" s="2">
+        <v>40565</v>
+      </c>
+      <c r="I64" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A65" t="s">
         <v>1415</v>
       </c>
@@ -7669,11 +7892,14 @@
       <c r="G65" t="s">
         <v>229</v>
       </c>
-      <c r="H65" t="s">
+      <c r="H65" s="2">
+        <v>40547</v>
+      </c>
+      <c r="I65" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A66" t="s">
         <v>1417</v>
       </c>
@@ -7695,11 +7921,14 @@
       <c r="G66" t="s">
         <v>232</v>
       </c>
-      <c r="H66" t="s">
+      <c r="H66" s="2">
+        <v>40472</v>
+      </c>
+      <c r="I66" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A67" t="s">
         <v>1419</v>
       </c>
@@ -7721,11 +7950,14 @@
       <c r="G67" t="s">
         <v>236</v>
       </c>
-      <c r="H67" t="s">
+      <c r="H67" s="2">
+        <v>40273</v>
+      </c>
+      <c r="I67" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A68" t="s">
         <v>1421</v>
       </c>
@@ -7747,11 +7979,14 @@
       <c r="G68" t="s">
         <v>239</v>
       </c>
-      <c r="H68" t="s">
+      <c r="H68" s="2">
+        <v>40554</v>
+      </c>
+      <c r="I68" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A69" t="s">
         <v>1423</v>
       </c>
@@ -7773,11 +8008,14 @@
       <c r="G69" t="s">
         <v>242</v>
       </c>
-      <c r="H69" t="s">
+      <c r="H69" s="2">
+        <v>40408</v>
+      </c>
+      <c r="I69" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A70" t="s">
         <v>1424</v>
       </c>
@@ -7799,11 +8037,14 @@
       <c r="G70" t="s">
         <v>245</v>
       </c>
-      <c r="H70" t="s">
+      <c r="H70" s="2">
+        <v>40515</v>
+      </c>
+      <c r="I70" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A71" t="s">
         <v>1425</v>
       </c>
@@ -7825,11 +8066,14 @@
       <c r="G71" t="s">
         <v>249</v>
       </c>
-      <c r="H71" t="s">
+      <c r="H71" s="2">
+        <v>40418</v>
+      </c>
+      <c r="I71" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A72" t="s">
         <v>1426</v>
       </c>
@@ -7851,11 +8095,14 @@
       <c r="G72" t="s">
         <v>252</v>
       </c>
-      <c r="H72" t="s">
+      <c r="H72" s="2">
+        <v>40452</v>
+      </c>
+      <c r="I72" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A73" t="s">
         <v>1427</v>
       </c>
@@ -7877,11 +8124,14 @@
       <c r="G73" t="s">
         <v>256</v>
       </c>
-      <c r="H73" t="s">
+      <c r="H73" s="2">
+        <v>40424</v>
+      </c>
+      <c r="I73" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A74" t="s">
         <v>1428</v>
       </c>
@@ -7903,11 +8153,14 @@
       <c r="G74" t="s">
         <v>259</v>
       </c>
-      <c r="H74" t="s">
+      <c r="H74" s="2">
+        <v>40411</v>
+      </c>
+      <c r="I74" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A75" t="s">
         <v>1429</v>
       </c>
@@ -7929,11 +8182,14 @@
       <c r="G75" t="s">
         <v>262</v>
       </c>
-      <c r="H75" t="s">
+      <c r="H75" s="2">
+        <v>40442</v>
+      </c>
+      <c r="I75" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A76" t="s">
         <v>1430</v>
       </c>
@@ -7955,11 +8211,14 @@
       <c r="G76" t="s">
         <v>265</v>
       </c>
-      <c r="H76" t="s">
+      <c r="H76" s="2">
+        <v>40507</v>
+      </c>
+      <c r="I76" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A77" t="s">
         <v>1431</v>
       </c>
@@ -7981,11 +8240,14 @@
       <c r="G77" t="s">
         <v>268</v>
       </c>
-      <c r="H77" t="s">
+      <c r="H77" s="2">
+        <v>40466</v>
+      </c>
+      <c r="I77" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A78" t="s">
         <v>1432</v>
       </c>
@@ -8007,11 +8269,14 @@
       <c r="G78" t="s">
         <v>271</v>
       </c>
-      <c r="H78" t="s">
+      <c r="H78" s="2">
+        <v>40347</v>
+      </c>
+      <c r="I78" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A79" t="s">
         <v>1433</v>
       </c>
@@ -8033,11 +8298,14 @@
       <c r="G79" t="s">
         <v>274</v>
       </c>
-      <c r="H79" t="s">
+      <c r="H79" s="2">
+        <v>40533</v>
+      </c>
+      <c r="I79" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A80" t="s">
         <v>1434</v>
       </c>
@@ -8059,11 +8327,14 @@
       <c r="G80" t="s">
         <v>277</v>
       </c>
-      <c r="H80" t="s">
+      <c r="H80" s="2">
+        <v>40469</v>
+      </c>
+      <c r="I80" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A81" t="s">
         <v>1435</v>
       </c>
@@ -8085,11 +8356,14 @@
       <c r="G81" t="s">
         <v>280</v>
       </c>
-      <c r="H81" t="s">
+      <c r="H81" s="2">
+        <v>40623</v>
+      </c>
+      <c r="I81" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A82" t="s">
         <v>1436</v>
       </c>
@@ -8111,11 +8385,14 @@
       <c r="G82" t="s">
         <v>283</v>
       </c>
-      <c r="H82" t="s">
+      <c r="H82" s="2">
+        <v>40421</v>
+      </c>
+      <c r="I82" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A83" t="s">
         <v>1437</v>
       </c>
@@ -8137,11 +8414,14 @@
       <c r="G83" t="s">
         <v>286</v>
       </c>
-      <c r="H83" t="s">
+      <c r="H83" s="2">
+        <v>40618</v>
+      </c>
+      <c r="I83" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A84" t="s">
         <v>1438</v>
       </c>
@@ -8163,11 +8443,14 @@
       <c r="G84" t="s">
         <v>289</v>
       </c>
-      <c r="H84" t="s">
+      <c r="H84" s="2">
+        <v>40420</v>
+      </c>
+      <c r="I84" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A85" t="s">
         <v>1439</v>
       </c>
@@ -8189,11 +8472,14 @@
       <c r="G85" t="s">
         <v>291</v>
       </c>
-      <c r="H85" t="s">
+      <c r="H85" s="2">
+        <v>40335</v>
+      </c>
+      <c r="I85" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A86" t="s">
         <v>1440</v>
       </c>
@@ -8215,11 +8501,14 @@
       <c r="G86" t="s">
         <v>294</v>
       </c>
-      <c r="H86" t="s">
+      <c r="H86" s="2">
+        <v>40575</v>
+      </c>
+      <c r="I86" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A87" t="s">
         <v>1441</v>
       </c>
@@ -8241,11 +8530,14 @@
       <c r="G87" t="s">
         <v>298</v>
       </c>
-      <c r="H87" t="s">
+      <c r="H87" s="2">
+        <v>40504</v>
+      </c>
+      <c r="I87" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A88" t="s">
         <v>1442</v>
       </c>
@@ -8267,11 +8559,14 @@
       <c r="G88" t="s">
         <v>301</v>
       </c>
-      <c r="H88" t="s">
+      <c r="H88" s="2">
+        <v>40398</v>
+      </c>
+      <c r="I88" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A89" t="s">
         <v>1443</v>
       </c>
@@ -8293,11 +8588,14 @@
       <c r="G89" t="s">
         <v>304</v>
       </c>
-      <c r="H89" t="s">
+      <c r="H89" s="2">
+        <v>40582</v>
+      </c>
+      <c r="I89" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A90" t="s">
         <v>1444</v>
       </c>
@@ -8319,11 +8617,14 @@
       <c r="G90" t="s">
         <v>307</v>
       </c>
-      <c r="H90" t="s">
+      <c r="H90" s="2">
+        <v>40614</v>
+      </c>
+      <c r="I90" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A91" t="s">
         <v>1445</v>
       </c>
@@ -8345,11 +8646,14 @@
       <c r="G91" t="s">
         <v>310</v>
       </c>
-      <c r="H91" t="s">
+      <c r="H91" s="2">
+        <v>40496</v>
+      </c>
+      <c r="I91" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A92" t="s">
         <v>1446</v>
       </c>
@@ -8371,11 +8675,14 @@
       <c r="G92" t="s">
         <v>314</v>
       </c>
-      <c r="H92" t="s">
+      <c r="H92" s="2">
+        <v>40527</v>
+      </c>
+      <c r="I92" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A93" t="s">
         <v>1447</v>
       </c>
@@ -8397,11 +8704,14 @@
       <c r="G93" t="s">
         <v>317</v>
       </c>
-      <c r="H93" t="s">
+      <c r="H93" s="2">
+        <v>40573</v>
+      </c>
+      <c r="I93" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A94" t="s">
         <v>1448</v>
       </c>
@@ -8423,11 +8733,14 @@
       <c r="G94" t="s">
         <v>320</v>
       </c>
-      <c r="H94" t="s">
+      <c r="H94" s="2">
+        <v>40298</v>
+      </c>
+      <c r="I94" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A95" t="s">
         <v>1449</v>
       </c>
@@ -8449,11 +8762,14 @@
       <c r="G95" t="s">
         <v>323</v>
       </c>
-      <c r="H95" t="s">
+      <c r="H95" s="2">
+        <v>40300</v>
+      </c>
+      <c r="I95" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A96" t="s">
         <v>1450</v>
       </c>
@@ -8475,11 +8791,14 @@
       <c r="G96" t="s">
         <v>326</v>
       </c>
-      <c r="H96" t="s">
+      <c r="H96" s="2">
+        <v>40394</v>
+      </c>
+      <c r="I96" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A97" t="s">
         <v>1451</v>
       </c>
@@ -8501,11 +8820,14 @@
       <c r="G97" t="s">
         <v>331</v>
       </c>
-      <c r="H97" t="s">
+      <c r="H97" s="2">
+        <v>40599</v>
+      </c>
+      <c r="I97" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A98" t="s">
         <v>1452</v>
       </c>
@@ -8527,11 +8849,14 @@
       <c r="G98" t="s">
         <v>333</v>
       </c>
-      <c r="H98" t="s">
+      <c r="H98" s="2">
+        <v>40530</v>
+      </c>
+      <c r="I98" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A99" t="s">
         <v>1453</v>
       </c>
@@ -8553,11 +8878,14 @@
       <c r="G99" t="s">
         <v>336</v>
       </c>
-      <c r="H99" t="s">
+      <c r="H99" s="2">
+        <v>40621</v>
+      </c>
+      <c r="I99" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A100" t="s">
         <v>1454</v>
       </c>
@@ -8579,11 +8907,14 @@
       <c r="G100" t="s">
         <v>339</v>
       </c>
-      <c r="H100" t="s">
+      <c r="H100" s="2">
+        <v>40383</v>
+      </c>
+      <c r="I100" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A101" t="s">
         <v>1455</v>
       </c>
@@ -8605,11 +8936,14 @@
       <c r="G101" t="s">
         <v>342</v>
       </c>
-      <c r="H101" t="s">
+      <c r="H101" s="2">
+        <v>40465</v>
+      </c>
+      <c r="I101" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A102" t="s">
         <v>1456</v>
       </c>
@@ -8631,11 +8965,14 @@
       <c r="G102" t="s">
         <v>345</v>
       </c>
-      <c r="H102" t="s">
+      <c r="H102" s="2">
+        <v>40359</v>
+      </c>
+      <c r="I102" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A103" t="s">
         <v>1457</v>
       </c>
@@ -8657,11 +8994,14 @@
       <c r="G103" t="s">
         <v>349</v>
       </c>
-      <c r="H103" t="s">
+      <c r="H103" s="2">
+        <v>40514</v>
+      </c>
+      <c r="I103" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A104" t="s">
         <v>1458</v>
       </c>
@@ -8683,11 +9023,14 @@
       <c r="G104" t="s">
         <v>351</v>
       </c>
-      <c r="H104" t="s">
+      <c r="H104" s="2">
+        <v>40283</v>
+      </c>
+      <c r="I104" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A105" t="s">
         <v>1460</v>
       </c>
@@ -8709,11 +9052,14 @@
       <c r="G105" t="s">
         <v>354</v>
       </c>
-      <c r="H105" t="s">
+      <c r="H105" s="2">
+        <v>40605</v>
+      </c>
+      <c r="I105" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A106" t="s">
         <v>1462</v>
       </c>
@@ -8735,11 +9081,14 @@
       <c r="G106" t="s">
         <v>356</v>
       </c>
-      <c r="H106" t="s">
+      <c r="H106" s="2">
+        <v>40519</v>
+      </c>
+      <c r="I106" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A107" t="s">
         <v>1463</v>
       </c>
@@ -8761,11 +9110,14 @@
       <c r="G107" t="s">
         <v>359</v>
       </c>
-      <c r="H107" t="s">
+      <c r="H107" s="2">
+        <v>40277</v>
+      </c>
+      <c r="I107" t="s">
         <v>360</v>
       </c>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A108" t="s">
         <v>1464</v>
       </c>
@@ -8787,11 +9139,14 @@
       <c r="G108" t="s">
         <v>363</v>
       </c>
-      <c r="H108" t="s">
+      <c r="H108" s="2">
+        <v>40389</v>
+      </c>
+      <c r="I108" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A109" t="s">
         <v>1465</v>
       </c>
@@ -8813,11 +9168,14 @@
       <c r="G109" t="s">
         <v>262</v>
       </c>
-      <c r="H109" t="s">
+      <c r="H109" s="2">
+        <v>40571</v>
+      </c>
+      <c r="I109" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A110" t="s">
         <v>1466</v>
       </c>
@@ -8839,11 +9197,14 @@
       <c r="G110" t="s">
         <v>368</v>
       </c>
-      <c r="H110" t="s">
+      <c r="H110" s="2">
+        <v>40493</v>
+      </c>
+      <c r="I110" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A111" t="s">
         <v>1467</v>
       </c>
@@ -8865,11 +9226,14 @@
       <c r="G111" t="s">
         <v>116</v>
       </c>
-      <c r="H111" t="s">
+      <c r="H111" s="2">
+        <v>40572</v>
+      </c>
+      <c r="I111" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A112" t="s">
         <v>1468</v>
       </c>
@@ -8891,11 +9255,14 @@
       <c r="G112" t="s">
         <v>280</v>
       </c>
-      <c r="H112" t="s">
+      <c r="H112" s="2">
+        <v>40285</v>
+      </c>
+      <c r="I112" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A113" t="s">
         <v>1469</v>
       </c>
@@ -8917,11 +9284,14 @@
       <c r="G113" t="s">
         <v>376</v>
       </c>
-      <c r="H113" t="s">
+      <c r="H113" s="2">
+        <v>40502</v>
+      </c>
+      <c r="I113" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A114" t="s">
         <v>1470</v>
       </c>
@@ -8943,11 +9313,14 @@
       <c r="G114" t="s">
         <v>145</v>
       </c>
-      <c r="H114" t="s">
+      <c r="H114" s="2">
+        <v>40523</v>
+      </c>
+      <c r="I114" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A115" t="s">
         <v>1471</v>
       </c>
@@ -8969,11 +9342,14 @@
       <c r="G115" t="s">
         <v>382</v>
       </c>
-      <c r="H115" t="s">
+      <c r="H115" s="2">
+        <v>40319</v>
+      </c>
+      <c r="I115" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A116" t="s">
         <v>1472</v>
       </c>
@@ -8995,11 +9371,14 @@
       <c r="G116" t="s">
         <v>385</v>
       </c>
-      <c r="H116" t="s">
+      <c r="H116" s="2">
+        <v>40356</v>
+      </c>
+      <c r="I116" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A117" t="s">
         <v>1473</v>
       </c>
@@ -9021,11 +9400,14 @@
       <c r="G117" t="s">
         <v>389</v>
       </c>
-      <c r="H117" t="s">
+      <c r="H117" s="2">
+        <v>40481</v>
+      </c>
+      <c r="I117" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A118" t="s">
         <v>1474</v>
       </c>
@@ -9047,11 +9429,14 @@
       <c r="G118" t="s">
         <v>392</v>
       </c>
-      <c r="H118" t="s">
+      <c r="H118" s="2">
+        <v>40452</v>
+      </c>
+      <c r="I118" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A119" t="s">
         <v>1475</v>
       </c>
@@ -9073,11 +9458,14 @@
       <c r="G119" t="s">
         <v>394</v>
       </c>
-      <c r="H119" t="s">
+      <c r="H119" s="2">
+        <v>40407</v>
+      </c>
+      <c r="I119" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A120" t="s">
         <v>1476</v>
       </c>
@@ -9099,11 +9487,14 @@
       <c r="G120" t="s">
         <v>397</v>
       </c>
-      <c r="H120" t="s">
+      <c r="H120" s="2">
+        <v>40501</v>
+      </c>
+      <c r="I120" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A121" t="s">
         <v>1477</v>
       </c>
@@ -9125,11 +9516,14 @@
       <c r="G121" t="s">
         <v>400</v>
       </c>
-      <c r="H121" t="s">
+      <c r="H121" s="2">
+        <v>40394</v>
+      </c>
+      <c r="I121" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A122" t="s">
         <v>1478</v>
       </c>
@@ -9151,11 +9545,14 @@
       <c r="G122" t="s">
         <v>402</v>
       </c>
-      <c r="H122" t="s">
+      <c r="H122" s="2">
+        <v>40609</v>
+      </c>
+      <c r="I122" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A123" t="s">
         <v>1479</v>
       </c>
@@ -9177,11 +9574,14 @@
       <c r="G123" t="s">
         <v>405</v>
       </c>
-      <c r="H123" t="s">
+      <c r="H123" s="2">
+        <v>40490</v>
+      </c>
+      <c r="I123" t="s">
         <v>406</v>
       </c>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="124" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A124" t="s">
         <v>1480</v>
       </c>
@@ -9203,11 +9603,14 @@
       <c r="G124" t="s">
         <v>409</v>
       </c>
-      <c r="H124" t="s">
+      <c r="H124" s="2">
+        <v>40421</v>
+      </c>
+      <c r="I124" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A125" t="s">
         <v>1481</v>
       </c>
@@ -9229,11 +9632,14 @@
       <c r="G125" t="s">
         <v>412</v>
       </c>
-      <c r="H125" t="s">
+      <c r="H125" s="2">
+        <v>40374</v>
+      </c>
+      <c r="I125" t="s">
         <v>413</v>
       </c>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A126" t="s">
         <v>1482</v>
       </c>
@@ -9255,11 +9661,14 @@
       <c r="G126" t="s">
         <v>415</v>
       </c>
-      <c r="H126" t="s">
+      <c r="H126" s="2">
+        <v>40388</v>
+      </c>
+      <c r="I126" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A127" t="s">
         <v>1483</v>
       </c>
@@ -9281,11 +9690,14 @@
       <c r="G127" t="s">
         <v>418</v>
       </c>
-      <c r="H127" t="s">
+      <c r="H127" s="2">
+        <v>40527</v>
+      </c>
+      <c r="I127" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A128" t="s">
         <v>1484</v>
       </c>
@@ -9307,11 +9719,14 @@
       <c r="G128" t="s">
         <v>422</v>
       </c>
-      <c r="H128" t="s">
+      <c r="H128" s="2">
+        <v>40317</v>
+      </c>
+      <c r="I128" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A129" t="s">
         <v>1485</v>
       </c>
@@ -9333,11 +9748,14 @@
       <c r="G129" t="s">
         <v>425</v>
       </c>
-      <c r="H129" t="s">
+      <c r="H129" s="2">
+        <v>40484</v>
+      </c>
+      <c r="I129" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A130" t="s">
         <v>1486</v>
       </c>
@@ -9359,11 +9777,14 @@
       <c r="G130" t="s">
         <v>428</v>
       </c>
-      <c r="H130" t="s">
+      <c r="H130" s="2">
+        <v>40305</v>
+      </c>
+      <c r="I130" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A131" t="s">
         <v>1487</v>
       </c>
@@ -9385,11 +9806,14 @@
       <c r="G131" t="s">
         <v>431</v>
       </c>
-      <c r="H131" t="s">
+      <c r="H131" s="2">
+        <v>40525</v>
+      </c>
+      <c r="I131" t="s">
         <v>432</v>
       </c>
     </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A132" t="s">
         <v>1488</v>
       </c>
@@ -9411,11 +9835,14 @@
       <c r="G132" t="s">
         <v>435</v>
       </c>
-      <c r="H132" t="s">
+      <c r="H132" s="2">
+        <v>40324</v>
+      </c>
+      <c r="I132" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A133" t="s">
         <v>1489</v>
       </c>
@@ -9437,11 +9864,14 @@
       <c r="G133" t="s">
         <v>438</v>
       </c>
-      <c r="H133" t="s">
+      <c r="H133" s="2">
+        <v>40539</v>
+      </c>
+      <c r="I133" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="134" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A134" t="s">
         <v>1490</v>
       </c>
@@ -9463,11 +9893,14 @@
       <c r="G134" t="s">
         <v>60</v>
       </c>
-      <c r="H134" t="s">
+      <c r="H134" s="2">
+        <v>40459</v>
+      </c>
+      <c r="I134" t="s">
         <v>413</v>
       </c>
     </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A135" t="s">
         <v>1491</v>
       </c>
@@ -9489,11 +9922,14 @@
       <c r="G135" t="s">
         <v>443</v>
       </c>
-      <c r="H135" t="s">
+      <c r="H135" s="2">
+        <v>40611</v>
+      </c>
+      <c r="I135" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A136" t="s">
         <v>1492</v>
       </c>
@@ -9515,11 +9951,14 @@
       <c r="G136" t="s">
         <v>446</v>
       </c>
-      <c r="H136" t="s">
+      <c r="H136" s="2">
+        <v>40312</v>
+      </c>
+      <c r="I136" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A137" t="s">
         <v>1493</v>
       </c>
@@ -9541,11 +9980,14 @@
       <c r="G137" t="s">
         <v>450</v>
       </c>
-      <c r="H137" t="s">
+      <c r="H137" s="2">
+        <v>40372</v>
+      </c>
+      <c r="I137" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A138" t="s">
         <v>1494</v>
       </c>
@@ -9567,11 +10009,14 @@
       <c r="G138" t="s">
         <v>452</v>
       </c>
-      <c r="H138" t="s">
+      <c r="H138" s="2">
+        <v>40352</v>
+      </c>
+      <c r="I138" t="s">
         <v>453</v>
       </c>
     </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="139" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A139" t="s">
         <v>1495</v>
       </c>
@@ -9593,11 +10038,14 @@
       <c r="G139" t="s">
         <v>454</v>
       </c>
-      <c r="H139" t="s">
+      <c r="H139" s="2">
+        <v>40399</v>
+      </c>
+      <c r="I139" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="140" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A140" t="s">
         <v>1496</v>
       </c>
@@ -9619,11 +10067,14 @@
       <c r="G140" t="s">
         <v>457</v>
       </c>
-      <c r="H140" t="s">
+      <c r="H140" s="2">
+        <v>40459</v>
+      </c>
+      <c r="I140" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="141" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A141" t="s">
         <v>1497</v>
       </c>
@@ -9645,11 +10096,14 @@
       <c r="G141" t="s">
         <v>462</v>
       </c>
-      <c r="H141" t="s">
+      <c r="H141" s="2">
+        <v>40586</v>
+      </c>
+      <c r="I141" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="142" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A142" t="s">
         <v>1498</v>
       </c>
@@ -9671,11 +10125,14 @@
       <c r="G142" t="s">
         <v>465</v>
       </c>
-      <c r="H142" t="s">
+      <c r="H142" s="2">
+        <v>40622</v>
+      </c>
+      <c r="I142" t="s">
         <v>466</v>
       </c>
     </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="143" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A143" t="s">
         <v>1500</v>
       </c>
@@ -9697,11 +10154,14 @@
       <c r="G143" t="s">
         <v>470</v>
       </c>
-      <c r="H143" t="s">
+      <c r="H143" s="2">
+        <v>40350</v>
+      </c>
+      <c r="I143" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="144" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A144" t="s">
         <v>1502</v>
       </c>
@@ -9723,11 +10183,14 @@
       <c r="G144" t="s">
         <v>473</v>
       </c>
-      <c r="H144" t="s">
+      <c r="H144" s="2">
+        <v>40330</v>
+      </c>
+      <c r="I144" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A145" t="s">
         <v>1504</v>
       </c>
@@ -9749,11 +10212,14 @@
       <c r="G145" t="s">
         <v>476</v>
       </c>
-      <c r="H145" t="s">
+      <c r="H145" s="2">
+        <v>40520</v>
+      </c>
+      <c r="I145" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="146" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A146" t="s">
         <v>1505</v>
       </c>
@@ -9775,11 +10241,14 @@
       <c r="G146" t="s">
         <v>479</v>
       </c>
-      <c r="H146" t="s">
+      <c r="H146" s="2">
+        <v>40369</v>
+      </c>
+      <c r="I146" t="s">
         <v>480</v>
       </c>
     </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A147" t="s">
         <v>1506</v>
       </c>
@@ -9801,11 +10270,14 @@
       <c r="G147" t="s">
         <v>483</v>
       </c>
-      <c r="H147" t="s">
+      <c r="H147" s="2">
+        <v>40364</v>
+      </c>
+      <c r="I147" t="s">
         <v>466</v>
       </c>
     </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A148" t="s">
         <v>1507</v>
       </c>
@@ -9827,11 +10299,14 @@
       <c r="G148" t="s">
         <v>486</v>
       </c>
-      <c r="H148" t="s">
+      <c r="H148" s="2">
+        <v>40518</v>
+      </c>
+      <c r="I148" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A149" t="s">
         <v>1508</v>
       </c>
@@ -9853,11 +10328,14 @@
       <c r="G149" t="s">
         <v>488</v>
       </c>
-      <c r="H149" t="s">
+      <c r="H149" s="2">
+        <v>40358</v>
+      </c>
+      <c r="I149" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="150" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A150" t="s">
         <v>1509</v>
       </c>
@@ -9879,11 +10357,14 @@
       <c r="G150" t="s">
         <v>418</v>
       </c>
-      <c r="H150" t="s">
+      <c r="H150" s="2">
+        <v>40553</v>
+      </c>
+      <c r="I150" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="151" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="151" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A151" t="s">
         <v>1510</v>
       </c>
@@ -9905,11 +10386,14 @@
       <c r="G151" t="s">
         <v>493</v>
       </c>
-      <c r="H151" t="s">
+      <c r="H151" s="2">
+        <v>40430</v>
+      </c>
+      <c r="I151" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="152" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="152" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A152" t="s">
         <v>1511</v>
       </c>
@@ -9931,11 +10415,14 @@
       <c r="G152" t="s">
         <v>496</v>
       </c>
-      <c r="H152" t="s">
+      <c r="H152" s="2">
+        <v>40421</v>
+      </c>
+      <c r="I152" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="153" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A153" t="s">
         <v>1512</v>
       </c>
@@ -9957,11 +10444,14 @@
       <c r="G153" t="s">
         <v>159</v>
       </c>
-      <c r="H153" t="s">
+      <c r="H153" s="2">
+        <v>40358</v>
+      </c>
+      <c r="I153" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="154" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="154" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A154" t="s">
         <v>1513</v>
       </c>
@@ -9983,11 +10473,14 @@
       <c r="G154" t="s">
         <v>23</v>
       </c>
-      <c r="H154" t="s">
+      <c r="H154" s="2">
+        <v>40479</v>
+      </c>
+      <c r="I154" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="155" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="155" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A155" t="s">
         <v>1514</v>
       </c>
@@ -10009,11 +10502,14 @@
       <c r="G155" t="s">
         <v>503</v>
       </c>
-      <c r="H155" t="s">
+      <c r="H155" s="2">
+        <v>40306</v>
+      </c>
+      <c r="I155" t="s">
         <v>504</v>
       </c>
     </row>
-    <row r="156" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="156" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A156" t="s">
         <v>1515</v>
       </c>
@@ -10035,11 +10531,14 @@
       <c r="G156" t="s">
         <v>508</v>
       </c>
-      <c r="H156" t="s">
+      <c r="H156" s="2">
+        <v>40326</v>
+      </c>
+      <c r="I156" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="157" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="157" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A157" t="s">
         <v>1516</v>
       </c>
@@ -10061,11 +10560,14 @@
       <c r="G157" t="s">
         <v>511</v>
       </c>
-      <c r="H157" t="s">
+      <c r="H157" s="2">
+        <v>40476</v>
+      </c>
+      <c r="I157" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="158" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="158" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A158" t="s">
         <v>1517</v>
       </c>
@@ -10087,11 +10589,14 @@
       <c r="G158" t="s">
         <v>514</v>
       </c>
-      <c r="H158" t="s">
+      <c r="H158" s="2">
+        <v>40398</v>
+      </c>
+      <c r="I158" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="159" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="159" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A159" t="s">
         <v>1518</v>
       </c>
@@ -10113,11 +10618,14 @@
       <c r="G159" t="s">
         <v>516</v>
       </c>
-      <c r="H159" t="s">
+      <c r="H159" s="2">
+        <v>40433</v>
+      </c>
+      <c r="I159" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="160" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="160" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A160" t="s">
         <v>1519</v>
       </c>
@@ -10139,11 +10647,14 @@
       <c r="G160" t="s">
         <v>520</v>
       </c>
-      <c r="H160" t="s">
+      <c r="H160" s="2">
+        <v>40537</v>
+      </c>
+      <c r="I160" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="161" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="161" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A161" t="s">
         <v>1520</v>
       </c>
@@ -10165,11 +10676,14 @@
       <c r="G161" t="s">
         <v>522</v>
       </c>
-      <c r="H161" t="s">
+      <c r="H161" s="2">
+        <v>40558</v>
+      </c>
+      <c r="I161" t="s">
         <v>466</v>
       </c>
     </row>
-    <row r="162" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="162" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A162" t="s">
         <v>1521</v>
       </c>
@@ -10191,11 +10705,14 @@
       <c r="G162" t="s">
         <v>525</v>
       </c>
-      <c r="H162" t="s">
+      <c r="H162" s="2">
+        <v>40506</v>
+      </c>
+      <c r="I162" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="163" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="163" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A163" t="s">
         <v>1522</v>
       </c>
@@ -10217,11 +10734,14 @@
       <c r="G163" t="s">
         <v>528</v>
       </c>
-      <c r="H163" t="s">
+      <c r="H163" s="2">
+        <v>40352</v>
+      </c>
+      <c r="I163" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="164" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="164" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A164" t="s">
         <v>1523</v>
       </c>
@@ -10243,11 +10763,14 @@
       <c r="G164" t="s">
         <v>531</v>
       </c>
-      <c r="H164" t="s">
+      <c r="H164" s="2">
+        <v>40592</v>
+      </c>
+      <c r="I164" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="165" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="165" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A165" t="s">
         <v>1524</v>
       </c>
@@ -10269,11 +10792,14 @@
       <c r="G165" t="s">
         <v>534</v>
       </c>
-      <c r="H165" t="s">
+      <c r="H165" s="2">
+        <v>40333</v>
+      </c>
+      <c r="I165" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="166" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="166" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A166" t="s">
         <v>1525</v>
       </c>
@@ -10295,11 +10821,14 @@
       <c r="G166" t="s">
         <v>538</v>
       </c>
-      <c r="H166" t="s">
+      <c r="H166" s="2">
+        <v>40464</v>
+      </c>
+      <c r="I166" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="167" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="167" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A167" t="s">
         <v>1526</v>
       </c>
@@ -10321,11 +10850,14 @@
       <c r="G167" t="s">
         <v>541</v>
       </c>
-      <c r="H167" t="s">
+      <c r="H167" s="2">
+        <v>40342</v>
+      </c>
+      <c r="I167" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="168" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="168" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A168" t="s">
         <v>1527</v>
       </c>
@@ -10347,11 +10879,14 @@
       <c r="G168" t="s">
         <v>544</v>
       </c>
-      <c r="H168" t="s">
+      <c r="H168" s="2">
+        <v>40592</v>
+      </c>
+      <c r="I168" t="s">
         <v>545</v>
       </c>
     </row>
-    <row r="169" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="169" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A169" t="s">
         <v>1528</v>
       </c>
@@ -10373,11 +10908,14 @@
       <c r="G169" t="s">
         <v>547</v>
       </c>
-      <c r="H169" t="s">
+      <c r="H169" s="2">
+        <v>40463</v>
+      </c>
+      <c r="I169" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="170" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="170" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A170" t="s">
         <v>1529</v>
       </c>
@@ -10399,11 +10937,14 @@
       <c r="G170" t="s">
         <v>549</v>
       </c>
-      <c r="H170" t="s">
+      <c r="H170" s="2">
+        <v>40579</v>
+      </c>
+      <c r="I170" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="171" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="171" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A171" t="s">
         <v>1530</v>
       </c>
@@ -10425,11 +10966,14 @@
       <c r="G171" t="s">
         <v>553</v>
       </c>
-      <c r="H171" t="s">
+      <c r="H171" s="2">
+        <v>40437</v>
+      </c>
+      <c r="I171" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="172" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="172" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A172" t="s">
         <v>1531</v>
       </c>
@@ -10451,11 +10995,14 @@
       <c r="G172" t="s">
         <v>556</v>
       </c>
-      <c r="H172" t="s">
+      <c r="H172" s="2">
+        <v>40413</v>
+      </c>
+      <c r="I172" t="s">
         <v>557</v>
       </c>
     </row>
-    <row r="173" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="173" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A173" t="s">
         <v>1532</v>
       </c>
@@ -10477,11 +11024,14 @@
       <c r="G173" t="s">
         <v>559</v>
       </c>
-      <c r="H173" t="s">
+      <c r="H173" s="2">
+        <v>40526</v>
+      </c>
+      <c r="I173" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="174" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="174" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A174" t="s">
         <v>1533</v>
       </c>
@@ -10503,11 +11053,14 @@
       <c r="G174" t="s">
         <v>525</v>
       </c>
-      <c r="H174" t="s">
+      <c r="H174" s="2">
+        <v>40558</v>
+      </c>
+      <c r="I174" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="175" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="175" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A175" t="s">
         <v>1534</v>
       </c>
@@ -10529,11 +11082,14 @@
       <c r="G175" t="s">
         <v>563</v>
       </c>
-      <c r="H175" t="s">
+      <c r="H175" s="2">
+        <v>40468</v>
+      </c>
+      <c r="I175" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="176" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="176" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A176" t="s">
         <v>1535</v>
       </c>
@@ -10555,11 +11111,14 @@
       <c r="G176" t="s">
         <v>525</v>
       </c>
-      <c r="H176" t="s">
+      <c r="H176" s="2">
+        <v>40460</v>
+      </c>
+      <c r="I176" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="177" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="177" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A177" t="s">
         <v>1536</v>
       </c>
@@ -10581,11 +11140,14 @@
       <c r="G177" t="s">
         <v>568</v>
       </c>
-      <c r="H177" t="s">
+      <c r="H177" s="2">
+        <v>40504</v>
+      </c>
+      <c r="I177" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="178" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="178" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A178" t="s">
         <v>1537</v>
       </c>
@@ -10607,11 +11169,14 @@
       <c r="G178" t="s">
         <v>571</v>
       </c>
-      <c r="H178" t="s">
+      <c r="H178" s="2">
+        <v>40504</v>
+      </c>
+      <c r="I178" t="s">
         <v>572</v>
       </c>
     </row>
-    <row r="179" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="179" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A179" t="s">
         <v>1538</v>
       </c>
@@ -10633,11 +11198,14 @@
       <c r="G179" t="s">
         <v>575</v>
       </c>
-      <c r="H179" t="s">
+      <c r="H179" s="2">
+        <v>40396</v>
+      </c>
+      <c r="I179" t="s">
         <v>576</v>
       </c>
     </row>
-    <row r="180" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="180" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A180" t="s">
         <v>1539</v>
       </c>
@@ -10659,11 +11227,14 @@
       <c r="G180" t="s">
         <v>579</v>
       </c>
-      <c r="H180" t="s">
+      <c r="H180" s="2">
+        <v>40386</v>
+      </c>
+      <c r="I180" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="181" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="181" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A181" t="s">
         <v>1540</v>
       </c>
@@ -10685,11 +11256,14 @@
       <c r="G181" t="s">
         <v>582</v>
       </c>
-      <c r="H181" t="s">
+      <c r="H181" s="2">
+        <v>40512</v>
+      </c>
+      <c r="I181" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="182" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="182" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A182" t="s">
         <v>1541</v>
       </c>
@@ -10711,11 +11285,14 @@
       <c r="G182" t="s">
         <v>585</v>
       </c>
-      <c r="H182" t="s">
+      <c r="H182" s="2">
+        <v>40347</v>
+      </c>
+      <c r="I182" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="183" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="183" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A183" t="s">
         <v>1542</v>
       </c>
@@ -10737,11 +11314,14 @@
       <c r="G183" t="s">
         <v>588</v>
       </c>
-      <c r="H183" t="s">
+      <c r="H183" s="2">
+        <v>40411</v>
+      </c>
+      <c r="I183" t="s">
         <v>589</v>
       </c>
     </row>
-    <row r="184" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="184" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A184" t="s">
         <v>1544</v>
       </c>
@@ -10763,11 +11343,14 @@
       <c r="G184" t="s">
         <v>592</v>
       </c>
-      <c r="H184" t="s">
+      <c r="H184" s="2">
+        <v>40539</v>
+      </c>
+      <c r="I184" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="185" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="185" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A185" t="s">
         <v>1545</v>
       </c>
@@ -10789,11 +11372,14 @@
       <c r="G185" t="s">
         <v>595</v>
       </c>
-      <c r="H185" t="s">
+      <c r="H185" s="2">
+        <v>40575</v>
+      </c>
+      <c r="I185" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="186" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="186" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A186" t="s">
         <v>1546</v>
       </c>
@@ -10815,11 +11401,14 @@
       <c r="G186" t="s">
         <v>409</v>
       </c>
-      <c r="H186" t="s">
+      <c r="H186" s="2">
+        <v>40346</v>
+      </c>
+      <c r="I186" t="s">
         <v>597</v>
       </c>
     </row>
-    <row r="187" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="187" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A187" t="s">
         <v>1547</v>
       </c>
@@ -10841,11 +11430,14 @@
       <c r="G187" t="s">
         <v>599</v>
       </c>
-      <c r="H187" t="s">
+      <c r="H187" s="2">
+        <v>40527</v>
+      </c>
+      <c r="I187" t="s">
         <v>600</v>
       </c>
     </row>
-    <row r="188" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="188" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A188" t="s">
         <v>1548</v>
       </c>
@@ -10867,11 +11459,14 @@
       <c r="G188" t="s">
         <v>603</v>
       </c>
-      <c r="H188" t="s">
+      <c r="H188" s="2">
+        <v>40305</v>
+      </c>
+      <c r="I188" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="189" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="189" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A189" t="s">
         <v>1549</v>
       </c>
@@ -10893,11 +11488,14 @@
       <c r="G189" t="s">
         <v>606</v>
       </c>
-      <c r="H189" t="s">
+      <c r="H189" s="2">
+        <v>40470</v>
+      </c>
+      <c r="I189" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="190" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="190" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A190" t="s">
         <v>1550</v>
       </c>
@@ -10919,11 +11517,14 @@
       <c r="G190" t="s">
         <v>609</v>
       </c>
-      <c r="H190" t="s">
+      <c r="H190" s="2">
+        <v>40464</v>
+      </c>
+      <c r="I190" t="s">
         <v>610</v>
       </c>
     </row>
-    <row r="191" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="191" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A191" t="s">
         <v>1551</v>
       </c>
@@ -10945,11 +11546,14 @@
       <c r="G191" t="s">
         <v>613</v>
       </c>
-      <c r="H191" t="s">
+      <c r="H191" s="2">
+        <v>40469</v>
+      </c>
+      <c r="I191" t="s">
         <v>480</v>
       </c>
     </row>
-    <row r="192" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="192" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A192" t="s">
         <v>1552</v>
       </c>
@@ -10971,11 +11575,14 @@
       <c r="G192" t="s">
         <v>616</v>
       </c>
-      <c r="H192" t="s">
+      <c r="H192" s="2">
+        <v>40308</v>
+      </c>
+      <c r="I192" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="193" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="193" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A193" t="s">
         <v>1553</v>
       </c>
@@ -10997,11 +11604,14 @@
       <c r="G193" t="s">
         <v>619</v>
       </c>
-      <c r="H193" t="s">
+      <c r="H193" s="2">
+        <v>40426</v>
+      </c>
+      <c r="I193" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="194" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="194" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A194" t="s">
         <v>1554</v>
       </c>
@@ -11023,11 +11633,14 @@
       <c r="G194" t="s">
         <v>621</v>
       </c>
-      <c r="H194" t="s">
+      <c r="H194" s="2">
+        <v>40487</v>
+      </c>
+      <c r="I194" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="195" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="195" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A195" t="s">
         <v>1555</v>
       </c>
@@ -11049,11 +11662,14 @@
       <c r="G195" t="s">
         <v>624</v>
       </c>
-      <c r="H195" t="s">
+      <c r="H195" s="2">
+        <v>40600</v>
+      </c>
+      <c r="I195" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="196" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="196" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A196" t="s">
         <v>1556</v>
       </c>
@@ -11075,11 +11691,14 @@
       <c r="G196" t="s">
         <v>627</v>
       </c>
-      <c r="H196" t="s">
+      <c r="H196" s="2">
+        <v>40292</v>
+      </c>
+      <c r="I196" t="s">
         <v>628</v>
       </c>
     </row>
-    <row r="197" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="197" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A197" t="s">
         <v>1557</v>
       </c>
@@ -11101,11 +11720,14 @@
       <c r="G197" t="s">
         <v>631</v>
       </c>
-      <c r="H197" t="s">
+      <c r="H197" s="2">
+        <v>40382</v>
+      </c>
+      <c r="I197" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="198" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="198" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A198" t="s">
         <v>1558</v>
       </c>
@@ -11127,11 +11749,14 @@
       <c r="G198" t="s">
         <v>633</v>
       </c>
-      <c r="H198" t="s">
+      <c r="H198" s="2">
+        <v>40359</v>
+      </c>
+      <c r="I198" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="199" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="199" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A199" t="s">
         <v>1559</v>
       </c>
@@ -11153,11 +11778,14 @@
       <c r="G199" t="s">
         <v>636</v>
       </c>
-      <c r="H199" t="s">
+      <c r="H199" s="2">
+        <v>40598</v>
+      </c>
+      <c r="I199" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="200" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="200" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A200" t="s">
         <v>1560</v>
       </c>
@@ -11179,11 +11807,14 @@
       <c r="G200" t="s">
         <v>639</v>
       </c>
-      <c r="H200" t="s">
+      <c r="H200" s="2">
+        <v>40299</v>
+      </c>
+      <c r="I200" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="201" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="201" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A201" t="s">
         <v>1561</v>
       </c>
@@ -11205,11 +11836,14 @@
       <c r="G201" t="s">
         <v>641</v>
       </c>
-      <c r="H201" t="s">
+      <c r="H201" s="2">
+        <v>40586</v>
+      </c>
+      <c r="I201" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="202" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="202" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A202" t="s">
         <v>1562</v>
       </c>
@@ -11231,11 +11865,14 @@
       <c r="G202" t="s">
         <v>643</v>
       </c>
-      <c r="H202" t="s">
+      <c r="H202" s="2">
+        <v>40409</v>
+      </c>
+      <c r="I202" t="s">
         <v>466</v>
       </c>
     </row>
-    <row r="203" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="203" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A203" t="s">
         <v>1563</v>
       </c>
@@ -11257,11 +11894,14 @@
       <c r="G203" t="s">
         <v>645</v>
       </c>
-      <c r="H203" t="s">
+      <c r="H203" s="2">
+        <v>40512</v>
+      </c>
+      <c r="I203" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="204" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="204" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A204" t="s">
         <v>1564</v>
       </c>
@@ -11283,11 +11923,14 @@
       <c r="G204" t="s">
         <v>648</v>
       </c>
-      <c r="H204" t="s">
+      <c r="H204" s="2">
+        <v>40413</v>
+      </c>
+      <c r="I204" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="205" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="205" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A205" t="s">
         <v>1565</v>
       </c>
@@ -11309,11 +11952,14 @@
       <c r="G205" t="s">
         <v>651</v>
       </c>
-      <c r="H205" t="s">
+      <c r="H205" s="2">
+        <v>40565</v>
+      </c>
+      <c r="I205" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="206" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="206" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A206" t="s">
         <v>1566</v>
       </c>
@@ -11335,11 +11981,14 @@
       <c r="G206" t="s">
         <v>654</v>
       </c>
-      <c r="H206" t="s">
+      <c r="H206" s="2">
+        <v>40547</v>
+      </c>
+      <c r="I206" t="s">
         <v>655</v>
       </c>
     </row>
-    <row r="207" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="207" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A207" t="s">
         <v>1567</v>
       </c>
@@ -11361,11 +12010,14 @@
       <c r="G207" t="s">
         <v>657</v>
       </c>
-      <c r="H207" t="s">
+      <c r="H207" s="2">
+        <v>40556</v>
+      </c>
+      <c r="I207" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="208" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="208" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A208" t="s">
         <v>1568</v>
       </c>
@@ -11387,11 +12039,14 @@
       <c r="G208" t="s">
         <v>660</v>
       </c>
-      <c r="H208" t="s">
+      <c r="H208" s="2">
+        <v>40303</v>
+      </c>
+      <c r="I208" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="209" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="209" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A209" t="s">
         <v>1569</v>
       </c>
@@ -11413,11 +12068,14 @@
       <c r="G209" t="s">
         <v>663</v>
       </c>
-      <c r="H209" t="s">
+      <c r="H209" s="2">
+        <v>40634</v>
+      </c>
+      <c r="I209" t="s">
         <v>655</v>
       </c>
     </row>
-    <row r="210" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="210" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A210" t="s">
         <v>1570</v>
       </c>
@@ -11439,11 +12097,14 @@
       <c r="G210" t="s">
         <v>667</v>
       </c>
-      <c r="H210" t="s">
+      <c r="H210" s="2">
+        <v>40497</v>
+      </c>
+      <c r="I210" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="211" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="211" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A211" t="s">
         <v>1571</v>
       </c>
@@ -11465,11 +12126,14 @@
       <c r="G211" t="s">
         <v>669</v>
       </c>
-      <c r="H211" t="s">
+      <c r="H211" s="2">
+        <v>40553</v>
+      </c>
+      <c r="I211" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="212" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="212" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A212" t="s">
         <v>1572</v>
       </c>
@@ -11491,11 +12155,14 @@
       <c r="G212" t="s">
         <v>672</v>
       </c>
-      <c r="H212" t="s">
+      <c r="H212" s="2">
+        <v>40572</v>
+      </c>
+      <c r="I212" t="s">
         <v>628</v>
       </c>
     </row>
-    <row r="213" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="213" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A213" t="s">
         <v>1573</v>
       </c>
@@ -11517,11 +12184,14 @@
       <c r="G213" t="s">
         <v>675</v>
       </c>
-      <c r="H213" t="s">
+      <c r="H213" s="2">
+        <v>40341</v>
+      </c>
+      <c r="I213" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="214" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="214" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A214" t="s">
         <v>1574</v>
       </c>
@@ -11543,11 +12213,14 @@
       <c r="G214" t="s">
         <v>678</v>
       </c>
-      <c r="H214" t="s">
+      <c r="H214" s="2">
+        <v>40605</v>
+      </c>
+      <c r="I214" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="215" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="215" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A215" t="s">
         <v>1575</v>
       </c>
@@ -11569,11 +12242,14 @@
       <c r="G215" t="s">
         <v>680</v>
       </c>
-      <c r="H215" t="s">
+      <c r="H215" s="2">
+        <v>40528</v>
+      </c>
+      <c r="I215" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="216" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="216" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A216" t="s">
         <v>1576</v>
       </c>
@@ -11595,11 +12271,14 @@
       <c r="G216" t="s">
         <v>10</v>
       </c>
-      <c r="H216" t="s">
+      <c r="H216" s="2">
+        <v>40540</v>
+      </c>
+      <c r="I216" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="217" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="217" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A217" t="s">
         <v>1577</v>
       </c>
@@ -11621,11 +12300,14 @@
       <c r="G217" t="s">
         <v>684</v>
       </c>
-      <c r="H217" t="s">
+      <c r="H217" s="2">
+        <v>40325</v>
+      </c>
+      <c r="I217" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="218" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="218" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A218" t="s">
         <v>1578</v>
       </c>
@@ -11647,11 +12329,14 @@
       <c r="G218" t="s">
         <v>687</v>
       </c>
-      <c r="H218" t="s">
+      <c r="H218" s="2">
+        <v>40438</v>
+      </c>
+      <c r="I218" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="219" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="219" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A219" t="s">
         <v>1579</v>
       </c>
@@ -11673,11 +12358,14 @@
       <c r="G219" t="s">
         <v>690</v>
       </c>
-      <c r="H219" t="s">
+      <c r="H219" s="2">
+        <v>40625</v>
+      </c>
+      <c r="I219" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="220" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="220" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A220" t="s">
         <v>1580</v>
       </c>
@@ -11699,11 +12387,14 @@
       <c r="G220" t="s">
         <v>691</v>
       </c>
-      <c r="H220" t="s">
+      <c r="H220" s="2">
+        <v>40527</v>
+      </c>
+      <c r="I220" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="221" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="221" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A221" t="s">
         <v>1581</v>
       </c>
@@ -11725,11 +12416,14 @@
       <c r="G221" t="s">
         <v>694</v>
       </c>
-      <c r="H221" t="s">
+      <c r="H221" s="2">
+        <v>40434</v>
+      </c>
+      <c r="I221" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="222" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="222" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A222" t="s">
         <v>1583</v>
       </c>
@@ -11751,11 +12445,14 @@
       <c r="G222" t="s">
         <v>696</v>
       </c>
-      <c r="H222" t="s">
+      <c r="H222" s="2">
+        <v>40475</v>
+      </c>
+      <c r="I222" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="223" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="223" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A223" t="s">
         <v>1584</v>
       </c>
@@ -11777,11 +12474,14 @@
       <c r="G223" t="s">
         <v>698</v>
       </c>
-      <c r="H223" t="s">
+      <c r="H223" s="2">
+        <v>40343</v>
+      </c>
+      <c r="I223" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="224" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="224" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A224" t="s">
         <v>1585</v>
       </c>
@@ -11803,11 +12503,14 @@
       <c r="G224" t="s">
         <v>422</v>
       </c>
-      <c r="H224" t="s">
+      <c r="H224" s="2">
+        <v>40482</v>
+      </c>
+      <c r="I224" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="225" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="225" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A225" t="s">
         <v>1586</v>
       </c>
@@ -11829,11 +12532,14 @@
       <c r="G225" t="s">
         <v>701</v>
       </c>
-      <c r="H225" t="s">
+      <c r="H225" s="2">
+        <v>40304</v>
+      </c>
+      <c r="I225" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="226" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="226" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A226" t="s">
         <v>1587</v>
       </c>
@@ -11855,11 +12561,14 @@
       <c r="G226" t="s">
         <v>703</v>
       </c>
-      <c r="H226" t="s">
+      <c r="H226" s="2">
+        <v>40517</v>
+      </c>
+      <c r="I226" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="227" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="227" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A227" t="s">
         <v>1588</v>
       </c>
@@ -11881,11 +12590,14 @@
       <c r="G227" t="s">
         <v>706</v>
       </c>
-      <c r="H227" t="s">
+      <c r="H227" s="2">
+        <v>40598</v>
+      </c>
+      <c r="I227" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="228" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="228" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A228" t="s">
         <v>1589</v>
       </c>
@@ -11907,11 +12619,14 @@
       <c r="G228" t="s">
         <v>159</v>
       </c>
-      <c r="H228" t="s">
+      <c r="H228" s="2">
+        <v>40556</v>
+      </c>
+      <c r="I228" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="229" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="229" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A229" t="s">
         <v>1590</v>
       </c>
@@ -11933,11 +12648,14 @@
       <c r="G229" t="s">
         <v>256</v>
       </c>
-      <c r="H229" t="s">
+      <c r="H229" s="2">
+        <v>40539</v>
+      </c>
+      <c r="I229" t="s">
         <v>466</v>
       </c>
     </row>
-    <row r="230" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="230" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A230" t="s">
         <v>1591</v>
       </c>
@@ -11959,11 +12677,14 @@
       <c r="G230" t="s">
         <v>713</v>
       </c>
-      <c r="H230" t="s">
+      <c r="H230" s="2">
+        <v>40386</v>
+      </c>
+      <c r="I230" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="231" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="231" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A231" t="s">
         <v>1592</v>
       </c>
@@ -11985,11 +12706,14 @@
       <c r="G231" t="s">
         <v>184</v>
       </c>
-      <c r="H231" t="s">
+      <c r="H231" s="2">
+        <v>40329</v>
+      </c>
+      <c r="I231" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="232" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="232" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A232" t="s">
         <v>1593</v>
       </c>
@@ -12011,11 +12735,14 @@
       <c r="G232" t="s">
         <v>716</v>
       </c>
-      <c r="H232" t="s">
+      <c r="H232" s="2">
+        <v>40502</v>
+      </c>
+      <c r="I232" t="s">
         <v>610</v>
       </c>
     </row>
-    <row r="233" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="233" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A233" t="s">
         <v>1594</v>
       </c>
@@ -12037,11 +12764,14 @@
       <c r="G233" t="s">
         <v>719</v>
       </c>
-      <c r="H233" t="s">
+      <c r="H233" s="2">
+        <v>40533</v>
+      </c>
+      <c r="I233" t="s">
         <v>720</v>
       </c>
     </row>
-    <row r="234" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="234" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A234" t="s">
         <v>1595</v>
       </c>
@@ -12063,11 +12793,14 @@
       <c r="G234" t="s">
         <v>723</v>
       </c>
-      <c r="H234" t="s">
+      <c r="H234" s="2">
+        <v>40321</v>
+      </c>
+      <c r="I234" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="235" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="235" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A235" t="s">
         <v>1596</v>
       </c>
@@ -12089,11 +12822,14 @@
       <c r="G235" t="s">
         <v>725</v>
       </c>
-      <c r="H235" t="s">
+      <c r="H235" s="2">
+        <v>40580</v>
+      </c>
+      <c r="I235" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="236" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="236" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A236" t="s">
         <v>1597</v>
       </c>
@@ -12115,11 +12851,14 @@
       <c r="G236" t="s">
         <v>727</v>
       </c>
-      <c r="H236" t="s">
+      <c r="H236" s="2">
+        <v>40578</v>
+      </c>
+      <c r="I236" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="237" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="237" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A237" t="s">
         <v>1598</v>
       </c>
@@ -12141,11 +12880,14 @@
       <c r="G237" t="s">
         <v>729</v>
       </c>
-      <c r="H237" t="s">
+      <c r="H237" s="2">
+        <v>40407</v>
+      </c>
+      <c r="I237" t="s">
         <v>480</v>
       </c>
     </row>
-    <row r="238" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="238" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A238" t="s">
         <v>1599</v>
       </c>
@@ -12167,11 +12909,14 @@
       <c r="G238" t="s">
         <v>732</v>
       </c>
-      <c r="H238" t="s">
+      <c r="H238" s="2">
+        <v>40275</v>
+      </c>
+      <c r="I238" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="239" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="239" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A239" t="s">
         <v>1600</v>
       </c>
@@ -12193,11 +12938,14 @@
       <c r="G239" t="s">
         <v>734</v>
       </c>
-      <c r="H239" t="s">
+      <c r="H239" s="2">
+        <v>40287</v>
+      </c>
+      <c r="I239" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="240" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="240" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A240" t="s">
         <v>1601</v>
       </c>
@@ -12219,11 +12967,14 @@
       <c r="G240" t="s">
         <v>737</v>
       </c>
-      <c r="H240" t="s">
+      <c r="H240" s="2">
+        <v>40410</v>
+      </c>
+      <c r="I240" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="241" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="241" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A241" t="s">
         <v>1602</v>
       </c>
@@ -12245,11 +12996,14 @@
       <c r="G241" t="s">
         <v>739</v>
       </c>
-      <c r="H241" t="s">
+      <c r="H241" s="2">
+        <v>40539</v>
+      </c>
+      <c r="I241" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="242" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="242" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A242" t="s">
         <v>1603</v>
       </c>
@@ -12271,11 +13025,14 @@
       <c r="G242" t="s">
         <v>743</v>
       </c>
-      <c r="H242" t="s">
+      <c r="H242" s="2">
+        <v>40277</v>
+      </c>
+      <c r="I242" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="243" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="243" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A243" t="s">
         <v>1604</v>
       </c>
@@ -12297,11 +13054,14 @@
       <c r="G243" t="s">
         <v>745</v>
       </c>
-      <c r="H243" t="s">
+      <c r="H243" s="2">
+        <v>40333</v>
+      </c>
+      <c r="I243" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="244" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="244" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A244" t="s">
         <v>1605</v>
       </c>
@@ -12323,11 +13083,14 @@
       <c r="G244" t="s">
         <v>748</v>
       </c>
-      <c r="H244" t="s">
+      <c r="H244" s="2">
+        <v>40278</v>
+      </c>
+      <c r="I244" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="245" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="245" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A245" t="s">
         <v>1606</v>
       </c>
@@ -12349,11 +13112,14 @@
       <c r="G245" t="s">
         <v>751</v>
       </c>
-      <c r="H245" t="s">
+      <c r="H245" s="2">
+        <v>40383</v>
+      </c>
+      <c r="I245" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="246" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="246" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A246" t="s">
         <v>1607</v>
       </c>
@@ -12375,11 +13141,14 @@
       <c r="G246" t="s">
         <v>754</v>
       </c>
-      <c r="H246" t="s">
+      <c r="H246" s="2">
+        <v>40441</v>
+      </c>
+      <c r="I246" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="247" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="247" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A247" t="s">
         <v>1608</v>
       </c>
@@ -12401,11 +13170,14 @@
       <c r="G247" t="s">
         <v>756</v>
       </c>
-      <c r="H247" t="s">
+      <c r="H247" s="2">
+        <v>40345</v>
+      </c>
+      <c r="I247" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="248" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="248" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A248" t="s">
         <v>1609</v>
       </c>
@@ -12427,11 +13199,14 @@
       <c r="G248" t="s">
         <v>758</v>
       </c>
-      <c r="H248" t="s">
+      <c r="H248" s="2">
+        <v>40312</v>
+      </c>
+      <c r="I248" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="249" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="249" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A249" t="s">
         <v>1610</v>
       </c>
@@ -12453,11 +13228,14 @@
       <c r="G249" t="s">
         <v>761</v>
       </c>
-      <c r="H249" t="s">
+      <c r="H249" s="2">
+        <v>40574</v>
+      </c>
+      <c r="I249" t="s">
         <v>610</v>
       </c>
     </row>
-    <row r="250" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="250" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A250" t="s">
         <v>1611</v>
       </c>
@@ -12479,11 +13257,14 @@
       <c r="G250" t="s">
         <v>764</v>
       </c>
-      <c r="H250" t="s">
+      <c r="H250" s="2">
+        <v>40406</v>
+      </c>
+      <c r="I250" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="251" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="251" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A251" t="s">
         <v>1612</v>
       </c>
@@ -12505,11 +13286,14 @@
       <c r="G251" t="s">
         <v>767</v>
       </c>
-      <c r="H251" t="s">
+      <c r="H251" s="2">
+        <v>40389</v>
+      </c>
+      <c r="I251" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="252" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="252" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A252" t="s">
         <v>1613</v>
       </c>
@@ -12531,11 +13315,14 @@
       <c r="G252" t="s">
         <v>769</v>
       </c>
-      <c r="H252" t="s">
+      <c r="H252" s="2">
+        <v>40278</v>
+      </c>
+      <c r="I252" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="253" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="253" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A253" t="s">
         <v>1614</v>
       </c>
@@ -12557,11 +13344,14 @@
       <c r="G253" t="s">
         <v>772</v>
       </c>
-      <c r="H253" t="s">
+      <c r="H253" s="2">
+        <v>40369</v>
+      </c>
+      <c r="I253" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="254" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="254" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A254" t="s">
         <v>1615</v>
       </c>
@@ -12583,11 +13373,14 @@
       <c r="G254" t="s">
         <v>775</v>
       </c>
-      <c r="H254" t="s">
+      <c r="H254" s="2">
+        <v>40477</v>
+      </c>
+      <c r="I254" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="255" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="255" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A255" t="s">
         <v>1616</v>
       </c>
@@ -12609,11 +13402,14 @@
       <c r="G255" t="s">
         <v>778</v>
       </c>
-      <c r="H255" t="s">
+      <c r="H255" s="2">
+        <v>40474</v>
+      </c>
+      <c r="I255" t="s">
         <v>779</v>
       </c>
     </row>
-    <row r="256" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="256" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A256" t="s">
         <v>1617</v>
       </c>
@@ -12635,11 +13431,14 @@
       <c r="G256" t="s">
         <v>781</v>
       </c>
-      <c r="H256" t="s">
+      <c r="H256" s="2">
+        <v>40584</v>
+      </c>
+      <c r="I256" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="257" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="257" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A257" t="s">
         <v>1618</v>
       </c>
@@ -12661,11 +13460,14 @@
       <c r="G257" t="s">
         <v>783</v>
       </c>
-      <c r="H257" t="s">
+      <c r="H257" s="2">
+        <v>40503</v>
+      </c>
+      <c r="I257" t="s">
         <v>784</v>
       </c>
     </row>
-    <row r="258" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="258" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A258" t="s">
         <v>1619</v>
       </c>
@@ -12687,11 +13489,14 @@
       <c r="G258" t="s">
         <v>788</v>
       </c>
-      <c r="H258" t="s">
+      <c r="H258" s="2">
+        <v>40436</v>
+      </c>
+      <c r="I258" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="259" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="259" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A259" t="s">
         <v>1620</v>
       </c>
@@ -12713,11 +13518,14 @@
       <c r="G259" t="s">
         <v>791</v>
       </c>
-      <c r="H259" t="s">
+      <c r="H259" s="2">
+        <v>40478</v>
+      </c>
+      <c r="I259" t="s">
         <v>610</v>
       </c>
     </row>
-    <row r="260" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="260" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A260" t="s">
         <v>1622</v>
       </c>
@@ -12739,11 +13547,14 @@
       <c r="G260" t="s">
         <v>793</v>
       </c>
-      <c r="H260" t="s">
+      <c r="H260" s="2">
+        <v>40582</v>
+      </c>
+      <c r="I260" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="261" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="261" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A261" t="s">
         <v>1623</v>
       </c>
@@ -12765,11 +13576,14 @@
       <c r="G261" t="s">
         <v>795</v>
       </c>
-      <c r="H261" t="s">
+      <c r="H261" s="2">
+        <v>40585</v>
+      </c>
+      <c r="I261" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="262" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="262" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A262" t="s">
         <v>1624</v>
       </c>
@@ -12791,11 +13605,14 @@
       <c r="G262" t="s">
         <v>798</v>
       </c>
-      <c r="H262" t="s">
+      <c r="H262" s="2">
+        <v>40500</v>
+      </c>
+      <c r="I262" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="263" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="263" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A263" t="s">
         <v>1625</v>
       </c>
@@ -12817,11 +13634,14 @@
       <c r="G263" t="s">
         <v>800</v>
       </c>
-      <c r="H263" t="s">
+      <c r="H263" s="2">
+        <v>40588</v>
+      </c>
+      <c r="I263" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="264" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="264" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A264" t="s">
         <v>1626</v>
       </c>
@@ -12843,11 +13663,14 @@
       <c r="G264" t="s">
         <v>803</v>
       </c>
-      <c r="H264" t="s">
+      <c r="H264" s="2">
+        <v>40395</v>
+      </c>
+      <c r="I264" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="265" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="265" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A265" t="s">
         <v>1627</v>
       </c>
@@ -12869,11 +13692,14 @@
       <c r="G265" t="s">
         <v>806</v>
       </c>
-      <c r="H265" t="s">
+      <c r="H265" s="2">
+        <v>40374</v>
+      </c>
+      <c r="I265" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="266" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="266" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A266" t="s">
         <v>1628</v>
       </c>
@@ -12895,11 +13721,14 @@
       <c r="G266" t="s">
         <v>809</v>
       </c>
-      <c r="H266" t="s">
+      <c r="H266" s="2">
+        <v>40592</v>
+      </c>
+      <c r="I266" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="267" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="267" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A267" t="s">
         <v>1629</v>
       </c>
@@ -12921,11 +13750,14 @@
       <c r="G267" t="s">
         <v>810</v>
       </c>
-      <c r="H267" t="s">
+      <c r="H267" s="2">
+        <v>40498</v>
+      </c>
+      <c r="I267" t="s">
         <v>466</v>
       </c>
     </row>
-    <row r="268" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="268" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A268" t="s">
         <v>1630</v>
       </c>
@@ -12947,11 +13779,14 @@
       <c r="G268" t="s">
         <v>813</v>
       </c>
-      <c r="H268" t="s">
+      <c r="H268" s="2">
+        <v>40383</v>
+      </c>
+      <c r="I268" t="s">
         <v>814</v>
       </c>
     </row>
-    <row r="269" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="269" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A269" t="s">
         <v>1631</v>
       </c>
@@ -12973,11 +13808,14 @@
       <c r="G269" t="s">
         <v>817</v>
       </c>
-      <c r="H269" t="s">
+      <c r="H269" s="2">
+        <v>40577</v>
+      </c>
+      <c r="I269" t="s">
         <v>818</v>
       </c>
     </row>
-    <row r="270" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="270" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A270" t="s">
         <v>1632</v>
       </c>
@@ -12999,11 +13837,14 @@
       <c r="G270" t="s">
         <v>820</v>
       </c>
-      <c r="H270" t="s">
+      <c r="H270" s="2">
+        <v>40533</v>
+      </c>
+      <c r="I270" t="s">
         <v>814</v>
       </c>
     </row>
-    <row r="271" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="271" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A271" t="s">
         <v>1633</v>
       </c>
@@ -13025,11 +13866,14 @@
       <c r="G271" t="s">
         <v>482</v>
       </c>
-      <c r="H271" t="s">
+      <c r="H271" s="2">
+        <v>40515</v>
+      </c>
+      <c r="I271" t="s">
         <v>822</v>
       </c>
     </row>
-    <row r="272" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="272" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A272" t="s">
         <v>1634</v>
       </c>
@@ -13051,11 +13895,14 @@
       <c r="G272" t="s">
         <v>159</v>
       </c>
-      <c r="H272" t="s">
+      <c r="H272" s="2">
+        <v>40579</v>
+      </c>
+      <c r="I272" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="273" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="273" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A273" t="s">
         <v>1635</v>
       </c>
@@ -13077,11 +13924,14 @@
       <c r="G273" t="s">
         <v>826</v>
       </c>
-      <c r="H273" t="s">
+      <c r="H273" s="2">
+        <v>40465</v>
+      </c>
+      <c r="I273" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="274" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="274" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A274" t="s">
         <v>1636</v>
       </c>
@@ -13103,11 +13953,14 @@
       <c r="G274" t="s">
         <v>392</v>
       </c>
-      <c r="H274" t="s">
+      <c r="H274" s="2">
+        <v>40408</v>
+      </c>
+      <c r="I274" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="275" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="275" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A275" t="s">
         <v>1637</v>
       </c>
@@ -13129,11 +13982,14 @@
       <c r="G275" t="s">
         <v>831</v>
       </c>
-      <c r="H275" t="s">
+      <c r="H275" s="2">
+        <v>40460</v>
+      </c>
+      <c r="I275" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="276" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="276" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A276" t="s">
         <v>1638</v>
       </c>
@@ -13155,11 +14011,14 @@
       <c r="G276" t="s">
         <v>833</v>
       </c>
-      <c r="H276" t="s">
+      <c r="H276" s="2">
+        <v>40390</v>
+      </c>
+      <c r="I276" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="277" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="277" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A277" t="s">
         <v>1639</v>
       </c>
@@ -13181,11 +14040,14 @@
       <c r="G277" t="s">
         <v>836</v>
       </c>
-      <c r="H277" t="s">
+      <c r="H277" s="2">
+        <v>40331</v>
+      </c>
+      <c r="I277" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="278" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="278" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A278" t="s">
         <v>1640</v>
       </c>
@@ -13207,11 +14069,14 @@
       <c r="G278" t="s">
         <v>838</v>
       </c>
-      <c r="H278" t="s">
+      <c r="H278" s="2">
+        <v>40432</v>
+      </c>
+      <c r="I278" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="279" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="279" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A279" t="s">
         <v>1641</v>
       </c>
@@ -13233,11 +14098,14 @@
       <c r="G279" t="s">
         <v>840</v>
       </c>
-      <c r="H279" t="s">
+      <c r="H279" s="2">
+        <v>40473</v>
+      </c>
+      <c r="I279" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="280" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="280" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A280" t="s">
         <v>1642</v>
       </c>
@@ -13259,11 +14127,14 @@
       <c r="G280" t="s">
         <v>841</v>
       </c>
-      <c r="H280" t="s">
+      <c r="H280" s="2">
+        <v>40482</v>
+      </c>
+      <c r="I280" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="281" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="281" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A281" t="s">
         <v>1643</v>
       </c>
@@ -13285,11 +14156,14 @@
       <c r="G281" t="s">
         <v>621</v>
       </c>
-      <c r="H281" t="s">
+      <c r="H281" s="2">
+        <v>40618</v>
+      </c>
+      <c r="I281" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="282" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="282" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A282" t="s">
         <v>1644</v>
       </c>
@@ -13311,11 +14185,14 @@
       <c r="G282" t="s">
         <v>846</v>
       </c>
-      <c r="H282" t="s">
+      <c r="H282" s="2">
+        <v>40455</v>
+      </c>
+      <c r="I282" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="283" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="283" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A283" t="s">
         <v>1645</v>
       </c>
@@ -13337,11 +14214,14 @@
       <c r="G283" t="s">
         <v>849</v>
       </c>
-      <c r="H283" t="s">
+      <c r="H283" s="2">
+        <v>40581</v>
+      </c>
+      <c r="I283" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="284" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="284" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A284" t="s">
         <v>1646</v>
       </c>
@@ -13363,11 +14243,14 @@
       <c r="G284" t="s">
         <v>851</v>
       </c>
-      <c r="H284" t="s">
+      <c r="H284" s="2">
+        <v>40316</v>
+      </c>
+      <c r="I284" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="285" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="285" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A285" t="s">
         <v>1647</v>
       </c>
@@ -13389,11 +14272,14 @@
       <c r="G285" t="s">
         <v>854</v>
       </c>
-      <c r="H285" t="s">
+      <c r="H285" s="2">
+        <v>40430</v>
+      </c>
+      <c r="I285" t="s">
         <v>855</v>
       </c>
     </row>
-    <row r="286" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="286" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A286" t="s">
         <v>1648</v>
       </c>
@@ -13415,11 +14301,14 @@
       <c r="G286" t="s">
         <v>435</v>
       </c>
-      <c r="H286" t="s">
+      <c r="H286" s="2">
+        <v>40318</v>
+      </c>
+      <c r="I286" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="287" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="287" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A287" t="s">
         <v>1649</v>
       </c>
@@ -13441,11 +14330,14 @@
       <c r="G287" t="s">
         <v>858</v>
       </c>
-      <c r="H287" t="s">
+      <c r="H287" s="2">
+        <v>40378</v>
+      </c>
+      <c r="I287" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="288" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="288" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A288" t="s">
         <v>1650</v>
       </c>
@@ -13467,11 +14359,14 @@
       <c r="G288" t="s">
         <v>861</v>
       </c>
-      <c r="H288" t="s">
+      <c r="H288" s="2">
+        <v>40493</v>
+      </c>
+      <c r="I288" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="289" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="289" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A289" t="s">
         <v>1651</v>
       </c>
@@ -13493,11 +14388,14 @@
       <c r="G289" t="s">
         <v>38</v>
       </c>
-      <c r="H289" t="s">
+      <c r="H289" s="2">
+        <v>40278</v>
+      </c>
+      <c r="I289" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="290" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="290" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A290" t="s">
         <v>1652</v>
       </c>
@@ -13519,11 +14417,14 @@
       <c r="G290" t="s">
         <v>867</v>
       </c>
-      <c r="H290" t="s">
+      <c r="H290" s="2">
+        <v>40549</v>
+      </c>
+      <c r="I290" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="291" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="291" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A291" t="s">
         <v>1653</v>
       </c>
@@ -13545,11 +14446,14 @@
       <c r="G291" t="s">
         <v>314</v>
       </c>
-      <c r="H291" t="s">
+      <c r="H291" s="2">
+        <v>40532</v>
+      </c>
+      <c r="I291" t="s">
         <v>869</v>
       </c>
     </row>
-    <row r="292" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="292" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A292" t="s">
         <v>1654</v>
       </c>
@@ -13571,11 +14475,14 @@
       <c r="G292" t="s">
         <v>376</v>
       </c>
-      <c r="H292" t="s">
+      <c r="H292" s="2">
+        <v>40489</v>
+      </c>
+      <c r="I292" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="293" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="293" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A293" t="s">
         <v>1655</v>
       </c>
@@ -13597,11 +14504,14 @@
       <c r="G293" t="s">
         <v>872</v>
       </c>
-      <c r="H293" t="s">
+      <c r="H293" s="2">
+        <v>40563</v>
+      </c>
+      <c r="I293" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="294" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="294" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A294" t="s">
         <v>1656</v>
       </c>
@@ -13623,11 +14533,14 @@
       <c r="G294" t="s">
         <v>197</v>
       </c>
-      <c r="H294" t="s">
+      <c r="H294" s="2">
+        <v>40483</v>
+      </c>
+      <c r="I294" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="295" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="295" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A295" t="s">
         <v>1657</v>
       </c>
@@ -13649,11 +14562,14 @@
       <c r="G295" t="s">
         <v>877</v>
       </c>
-      <c r="H295" t="s">
+      <c r="H295" s="2">
+        <v>40542</v>
+      </c>
+      <c r="I295" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="296" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="296" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A296" t="s">
         <v>1658</v>
       </c>
@@ -13675,11 +14591,14 @@
       <c r="G296" t="s">
         <v>879</v>
       </c>
-      <c r="H296" t="s">
+      <c r="H296" s="2">
+        <v>40378</v>
+      </c>
+      <c r="I296" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="297" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="297" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A297" t="s">
         <v>1660</v>
       </c>
@@ -13701,11 +14620,14 @@
       <c r="G297" t="s">
         <v>881</v>
       </c>
-      <c r="H297" t="s">
+      <c r="H297" s="2">
+        <v>40337</v>
+      </c>
+      <c r="I297" t="s">
         <v>480</v>
       </c>
     </row>
-    <row r="298" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="298" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A298" t="s">
         <v>1661</v>
       </c>
@@ -13727,11 +14649,14 @@
       <c r="G298" t="s">
         <v>883</v>
       </c>
-      <c r="H298" t="s">
+      <c r="H298" s="2">
+        <v>40399</v>
+      </c>
+      <c r="I298" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="299" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="299" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A299" t="s">
         <v>1662</v>
       </c>
@@ -13753,11 +14678,14 @@
       <c r="G299" t="s">
         <v>885</v>
       </c>
-      <c r="H299" t="s">
+      <c r="H299" s="2">
+        <v>40545</v>
+      </c>
+      <c r="I299" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="300" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="300" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A300" t="s">
         <v>1663</v>
       </c>
@@ -13779,11 +14707,14 @@
       <c r="G300" t="s">
         <v>887</v>
       </c>
-      <c r="H300" t="s">
+      <c r="H300" s="2">
+        <v>40488</v>
+      </c>
+      <c r="I300" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="301" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="301" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A301" t="s">
         <v>1664</v>
       </c>
@@ -13805,11 +14736,14 @@
       <c r="G301" t="s">
         <v>889</v>
       </c>
-      <c r="H301" t="s">
+      <c r="H301" s="2">
+        <v>40619</v>
+      </c>
+      <c r="I301" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="302" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="302" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A302" t="s">
         <v>1665</v>
       </c>
@@ -13831,11 +14765,14 @@
       <c r="G302" t="s">
         <v>892</v>
       </c>
-      <c r="H302" t="s">
+      <c r="H302" s="2">
+        <v>40477</v>
+      </c>
+      <c r="I302" t="s">
         <v>893</v>
       </c>
     </row>
-    <row r="303" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="303" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A303" t="s">
         <v>1666</v>
       </c>
@@ -13857,11 +14794,14 @@
       <c r="G303" t="s">
         <v>895</v>
       </c>
-      <c r="H303" t="s">
+      <c r="H303" s="2">
+        <v>40572</v>
+      </c>
+      <c r="I303" t="s">
         <v>896</v>
       </c>
     </row>
-    <row r="304" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="304" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A304" t="s">
         <v>1667</v>
       </c>
@@ -13883,11 +14823,14 @@
       <c r="G304" t="s">
         <v>898</v>
       </c>
-      <c r="H304" t="s">
+      <c r="H304" s="2">
+        <v>40536</v>
+      </c>
+      <c r="I304" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="305" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="305" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A305" t="s">
         <v>1668</v>
       </c>
@@ -13909,11 +14852,14 @@
       <c r="G305" t="s">
         <v>901</v>
       </c>
-      <c r="H305" t="s">
+      <c r="H305" s="2">
+        <v>40568</v>
+      </c>
+      <c r="I305" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="306" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="306" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A306" t="s">
         <v>1669</v>
       </c>
@@ -13935,11 +14881,14 @@
       <c r="G306" t="s">
         <v>904</v>
       </c>
-      <c r="H306" t="s">
+      <c r="H306" s="2">
+        <v>40432</v>
+      </c>
+      <c r="I306" t="s">
         <v>413</v>
       </c>
     </row>
-    <row r="307" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="307" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A307" t="s">
         <v>1670</v>
       </c>
@@ -13961,11 +14910,14 @@
       <c r="G307" t="s">
         <v>907</v>
       </c>
-      <c r="H307" t="s">
+      <c r="H307" s="2">
+        <v>40408</v>
+      </c>
+      <c r="I307" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="308" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="308" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A308" t="s">
         <v>1671</v>
       </c>
@@ -13987,11 +14939,14 @@
       <c r="G308" t="s">
         <v>910</v>
       </c>
-      <c r="H308" t="s">
+      <c r="H308" s="2">
+        <v>40345</v>
+      </c>
+      <c r="I308" t="s">
         <v>911</v>
       </c>
     </row>
-    <row r="309" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="309" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A309" t="s">
         <v>1672</v>
       </c>
@@ -14013,11 +14968,14 @@
       <c r="G309" t="s">
         <v>913</v>
       </c>
-      <c r="H309" t="s">
+      <c r="H309" s="2">
+        <v>40567</v>
+      </c>
+      <c r="I309" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="310" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="310" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A310" t="s">
         <v>1673</v>
       </c>
@@ -14039,11 +14997,14 @@
       <c r="G310" t="s">
         <v>525</v>
       </c>
-      <c r="H310" t="s">
+      <c r="H310" s="2">
+        <v>40396</v>
+      </c>
+      <c r="I310" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="311" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="311" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A311" t="s">
         <v>1674</v>
       </c>
@@ -14065,11 +15026,14 @@
       <c r="G311" t="s">
         <v>919</v>
       </c>
-      <c r="H311" t="s">
+      <c r="H311" s="2">
+        <v>40409</v>
+      </c>
+      <c r="I311" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="312" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="312" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A312" t="s">
         <v>1675</v>
       </c>
@@ -14091,11 +15055,14 @@
       <c r="G312" t="s">
         <v>920</v>
       </c>
-      <c r="H312" t="s">
+      <c r="H312" s="2">
+        <v>40387</v>
+      </c>
+      <c r="I312" t="s">
         <v>545</v>
       </c>
     </row>
-    <row r="313" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="313" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A313" t="s">
         <v>1676</v>
       </c>
@@ -14117,11 +15084,14 @@
       <c r="G313" t="s">
         <v>923</v>
       </c>
-      <c r="H313" t="s">
+      <c r="H313" s="2">
+        <v>40354</v>
+      </c>
+      <c r="I313" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="314" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="314" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A314" t="s">
         <v>1677</v>
       </c>
@@ -14143,11 +15113,14 @@
       <c r="G314" t="s">
         <v>924</v>
       </c>
-      <c r="H314" t="s">
+      <c r="H314" s="2">
+        <v>40423</v>
+      </c>
+      <c r="I314" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="315" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="315" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A315" t="s">
         <v>1678</v>
       </c>
@@ -14169,11 +15142,14 @@
       <c r="G315" t="s">
         <v>927</v>
       </c>
-      <c r="H315" t="s">
+      <c r="H315" s="2">
+        <v>40611</v>
+      </c>
+      <c r="I315" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="316" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="316" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A316" t="s">
         <v>1679</v>
       </c>
@@ -14195,11 +15171,14 @@
       <c r="G316" t="s">
         <v>930</v>
       </c>
-      <c r="H316" t="s">
+      <c r="H316" s="2">
+        <v>40438</v>
+      </c>
+      <c r="I316" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="317" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="317" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A317" t="s">
         <v>1680</v>
       </c>
@@ -14221,11 +15200,14 @@
       <c r="G317" t="s">
         <v>891</v>
       </c>
-      <c r="H317" t="s">
+      <c r="H317" s="2">
+        <v>40282</v>
+      </c>
+      <c r="I317" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="318" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="318" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A318" t="s">
         <v>1681</v>
       </c>
@@ -14247,11 +15229,14 @@
       <c r="G318" t="s">
         <v>933</v>
       </c>
-      <c r="H318" t="s">
+      <c r="H318" s="2">
+        <v>40559</v>
+      </c>
+      <c r="I318" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="319" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="319" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A319" t="s">
         <v>1682</v>
       </c>
@@ -14273,11 +15258,14 @@
       <c r="G319" t="s">
         <v>935</v>
       </c>
-      <c r="H319" t="s">
+      <c r="H319" s="2">
+        <v>40425</v>
+      </c>
+      <c r="I319" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="320" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="320" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A320" t="s">
         <v>1683</v>
       </c>
@@ -14299,11 +15287,14 @@
       <c r="G320" t="s">
         <v>938</v>
       </c>
-      <c r="H320" t="s">
+      <c r="H320" s="2">
+        <v>40298</v>
+      </c>
+      <c r="I320" t="s">
         <v>504</v>
       </c>
     </row>
-    <row r="321" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="321" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A321" t="s">
         <v>1684</v>
       </c>
@@ -14325,11 +15316,14 @@
       <c r="G321" t="s">
         <v>941</v>
       </c>
-      <c r="H321" t="s">
+      <c r="H321" s="2">
+        <v>40456</v>
+      </c>
+      <c r="I321" t="s">
         <v>466</v>
       </c>
     </row>
-    <row r="322" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="322" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A322" t="s">
         <v>1685</v>
       </c>
@@ -14351,11 +15345,14 @@
       <c r="G322" t="s">
         <v>944</v>
       </c>
-      <c r="H322" t="s">
+      <c r="H322" s="2">
+        <v>40567</v>
+      </c>
+      <c r="I322" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="323" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="323" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A323" t="s">
         <v>1686</v>
       </c>
@@ -14377,11 +15374,14 @@
       <c r="G323" t="s">
         <v>946</v>
       </c>
-      <c r="H323" t="s">
+      <c r="H323" s="2">
+        <v>40463</v>
+      </c>
+      <c r="I323" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="324" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="324" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A324" t="s">
         <v>1687</v>
       </c>
@@ -14403,11 +15403,14 @@
       <c r="G324" t="s">
         <v>949</v>
       </c>
-      <c r="H324" t="s">
+      <c r="H324" s="2">
+        <v>40400</v>
+      </c>
+      <c r="I324" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="325" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="325" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A325" t="s">
         <v>1688</v>
       </c>
@@ -14429,11 +15432,14 @@
       <c r="G325" t="s">
         <v>952</v>
       </c>
-      <c r="H325" t="s">
+      <c r="H325" s="2">
+        <v>40329</v>
+      </c>
+      <c r="I325" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="326" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="326" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A326" t="s">
         <v>1689</v>
       </c>
@@ -14455,11 +15461,14 @@
       <c r="G326" t="s">
         <v>955</v>
       </c>
-      <c r="H326" t="s">
+      <c r="H326" s="2">
+        <v>40432</v>
+      </c>
+      <c r="I326" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="327" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="327" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A327" t="s">
         <v>1690</v>
       </c>
@@ -14481,11 +15490,14 @@
       <c r="G327" t="s">
         <v>957</v>
       </c>
-      <c r="H327" t="s">
+      <c r="H327" s="2">
+        <v>40501</v>
+      </c>
+      <c r="I327" t="s">
         <v>958</v>
       </c>
     </row>
-    <row r="328" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="328" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A328" t="s">
         <v>1691</v>
       </c>
@@ -14507,11 +15519,14 @@
       <c r="G328" t="s">
         <v>960</v>
       </c>
-      <c r="H328" t="s">
+      <c r="H328" s="2">
+        <v>40530</v>
+      </c>
+      <c r="I328" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="329" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="329" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A329" t="s">
         <v>1692</v>
       </c>
@@ -14533,11 +15548,14 @@
       <c r="G329" t="s">
         <v>963</v>
       </c>
-      <c r="H329" t="s">
+      <c r="H329" s="2">
+        <v>40477</v>
+      </c>
+      <c r="I329" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="330" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="330" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A330" t="s">
         <v>1693</v>
       </c>
@@ -14559,11 +15577,14 @@
       <c r="G330" t="s">
         <v>965</v>
       </c>
-      <c r="H330" t="s">
+      <c r="H330" s="2">
+        <v>40499</v>
+      </c>
+      <c r="I330" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="331" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="331" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A331" t="s">
         <v>1694</v>
       </c>
@@ -14585,11 +15606,14 @@
       <c r="G331" t="s">
         <v>968</v>
       </c>
-      <c r="H331" t="s">
+      <c r="H331" s="2">
+        <v>40335</v>
+      </c>
+      <c r="I331" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="332" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="332" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A332" t="s">
         <v>1695</v>
       </c>
@@ -14611,11 +15635,14 @@
       <c r="G332" t="s">
         <v>50</v>
       </c>
-      <c r="H332" t="s">
+      <c r="H332" s="2">
+        <v>40344</v>
+      </c>
+      <c r="I332" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="333" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="333" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A333" t="s">
         <v>1696</v>
       </c>
@@ -14637,11 +15664,14 @@
       <c r="G333" t="s">
         <v>972</v>
       </c>
-      <c r="H333" t="s">
+      <c r="H333" s="2">
+        <v>40448</v>
+      </c>
+      <c r="I333" t="s">
         <v>911</v>
       </c>
     </row>
-    <row r="334" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="334" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A334" t="s">
         <v>1698</v>
       </c>
@@ -14663,11 +15693,14 @@
       <c r="G334" t="s">
         <v>974</v>
       </c>
-      <c r="H334" t="s">
+      <c r="H334" s="2">
+        <v>40459</v>
+      </c>
+      <c r="I334" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="335" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="335" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A335" t="s">
         <v>1699</v>
       </c>
@@ -14689,11 +15722,14 @@
       <c r="G335" t="s">
         <v>976</v>
       </c>
-      <c r="H335" t="s">
+      <c r="H335" s="2">
+        <v>40417</v>
+      </c>
+      <c r="I335" t="s">
         <v>818</v>
       </c>
     </row>
-    <row r="336" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="336" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A336" t="s">
         <v>1700</v>
       </c>
@@ -14715,11 +15751,14 @@
       <c r="G336" t="s">
         <v>978</v>
       </c>
-      <c r="H336" t="s">
+      <c r="H336" s="2">
+        <v>40395</v>
+      </c>
+      <c r="I336" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="337" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="337" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A337" t="s">
         <v>1701</v>
       </c>
@@ -14741,11 +15780,14 @@
       <c r="G337" t="s">
         <v>981</v>
       </c>
-      <c r="H337" t="s">
+      <c r="H337" s="2">
+        <v>40386</v>
+      </c>
+      <c r="I337" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="338" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="338" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A338" t="s">
         <v>1702</v>
       </c>
@@ -14767,11 +15809,14 @@
       <c r="G338" t="s">
         <v>985</v>
       </c>
-      <c r="H338" t="s">
+      <c r="H338" s="2">
+        <v>40281</v>
+      </c>
+      <c r="I338" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="339" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="339" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A339" t="s">
         <v>1703</v>
       </c>
@@ -14793,11 +15838,14 @@
       <c r="G339" t="s">
         <v>988</v>
       </c>
-      <c r="H339" t="s">
+      <c r="H339" s="2">
+        <v>40369</v>
+      </c>
+      <c r="I339" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="340" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="340" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A340" t="s">
         <v>1704</v>
       </c>
@@ -14819,11 +15867,14 @@
       <c r="G340" t="s">
         <v>990</v>
       </c>
-      <c r="H340" t="s">
+      <c r="H340" s="2">
+        <v>40485</v>
+      </c>
+      <c r="I340" t="s">
         <v>911</v>
       </c>
     </row>
-    <row r="341" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="341" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A341" t="s">
         <v>1705</v>
       </c>
@@ -14845,11 +15896,14 @@
       <c r="G341" t="s">
         <v>993</v>
       </c>
-      <c r="H341" t="s">
+      <c r="H341" s="2">
+        <v>40480</v>
+      </c>
+      <c r="I341" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="342" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="342" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A342" t="s">
         <v>1706</v>
       </c>
@@ -14871,11 +15925,14 @@
       <c r="G342" t="s">
         <v>994</v>
       </c>
-      <c r="H342" t="s">
+      <c r="H342" s="2">
+        <v>40587</v>
+      </c>
+      <c r="I342" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="343" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="343" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A343" t="s">
         <v>1707</v>
       </c>
@@ -14897,11 +15954,14 @@
       <c r="G343" t="s">
         <v>997</v>
       </c>
-      <c r="H343" t="s">
+      <c r="H343" s="2">
+        <v>40369</v>
+      </c>
+      <c r="I343" t="s">
         <v>998</v>
       </c>
     </row>
-    <row r="344" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="344" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A344" t="s">
         <v>1708</v>
       </c>
@@ -14923,11 +15983,14 @@
       <c r="G344" t="s">
         <v>1001</v>
       </c>
-      <c r="H344" t="s">
+      <c r="H344" s="2">
+        <v>40591</v>
+      </c>
+      <c r="I344" t="s">
         <v>466</v>
       </c>
     </row>
-    <row r="345" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="345" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A345" t="s">
         <v>1709</v>
       </c>
@@ -14949,11 +16012,14 @@
       <c r="G345" t="s">
         <v>1004</v>
       </c>
-      <c r="H345" t="s">
+      <c r="H345" s="2">
+        <v>40548</v>
+      </c>
+      <c r="I345" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="346" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="346" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A346" t="s">
         <v>1710</v>
       </c>
@@ -14975,11 +16041,14 @@
       <c r="G346" t="s">
         <v>116</v>
       </c>
-      <c r="H346" t="s">
+      <c r="H346" s="2">
+        <v>40534</v>
+      </c>
+      <c r="I346" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="347" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="347" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A347" t="s">
         <v>1711</v>
       </c>
@@ -15001,11 +16070,14 @@
       <c r="G347" t="s">
         <v>1008</v>
       </c>
-      <c r="H347" t="s">
+      <c r="H347" s="2">
+        <v>40593</v>
+      </c>
+      <c r="I347" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="348" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="348" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A348" t="s">
         <v>1712</v>
       </c>
@@ -15027,11 +16099,14 @@
       <c r="G348" t="s">
         <v>1010</v>
       </c>
-      <c r="H348" t="s">
+      <c r="H348" s="2">
+        <v>40417</v>
+      </c>
+      <c r="I348" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="349" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="349" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A349" t="s">
         <v>1713</v>
       </c>
@@ -15053,11 +16128,14 @@
       <c r="G349" t="s">
         <v>1013</v>
       </c>
-      <c r="H349" t="s">
+      <c r="H349" s="2">
+        <v>40365</v>
+      </c>
+      <c r="I349" t="s">
         <v>1014</v>
       </c>
     </row>
-    <row r="350" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="350" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A350" t="s">
         <v>1714</v>
       </c>
@@ -15079,11 +16157,14 @@
       <c r="G350" t="s">
         <v>1017</v>
       </c>
-      <c r="H350" t="s">
+      <c r="H350" s="2">
+        <v>40364</v>
+      </c>
+      <c r="I350" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="351" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="351" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A351" t="s">
         <v>1715</v>
       </c>
@@ -15105,11 +16186,14 @@
       <c r="G351" t="s">
         <v>232</v>
       </c>
-      <c r="H351" t="s">
+      <c r="H351" s="2">
+        <v>40522</v>
+      </c>
+      <c r="I351" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="352" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="352" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A352" t="s">
         <v>1716</v>
       </c>
@@ -15131,11 +16215,14 @@
       <c r="G352" t="s">
         <v>1020</v>
       </c>
-      <c r="H352" t="s">
+      <c r="H352" s="2">
+        <v>40538</v>
+      </c>
+      <c r="I352" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="353" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="353" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A353" t="s">
         <v>1717</v>
       </c>
@@ -15157,11 +16244,14 @@
       <c r="G353" t="s">
         <v>1021</v>
       </c>
-      <c r="H353" t="s">
+      <c r="H353" s="2">
+        <v>40417</v>
+      </c>
+      <c r="I353" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="354" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="354" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A354" t="s">
         <v>1718</v>
       </c>
@@ -15183,11 +16273,14 @@
       <c r="G354" t="s">
         <v>817</v>
       </c>
-      <c r="H354" t="s">
+      <c r="H354" s="2">
+        <v>40586</v>
+      </c>
+      <c r="I354" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="355" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="355" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A355" t="s">
         <v>1719</v>
       </c>
@@ -15209,11 +16302,14 @@
       <c r="G355" t="s">
         <v>1026</v>
       </c>
-      <c r="H355" t="s">
+      <c r="H355" s="2">
+        <v>40335</v>
+      </c>
+      <c r="I355" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="356" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="356" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A356" t="s">
         <v>1720</v>
       </c>
@@ -15235,11 +16331,14 @@
       <c r="G356" t="s">
         <v>294</v>
       </c>
-      <c r="H356" t="s">
+      <c r="H356" s="2">
+        <v>40407</v>
+      </c>
+      <c r="I356" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="357" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="357" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A357" t="s">
         <v>1721</v>
       </c>
@@ -15261,11 +16360,14 @@
       <c r="G357" t="s">
         <v>1031</v>
       </c>
-      <c r="H357" t="s">
+      <c r="H357" s="2">
+        <v>40350</v>
+      </c>
+      <c r="I357" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="358" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="358" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A358" t="s">
         <v>1722</v>
       </c>
@@ -15287,11 +16389,14 @@
       <c r="G358" t="s">
         <v>1034</v>
       </c>
-      <c r="H358" t="s">
+      <c r="H358" s="2">
+        <v>40507</v>
+      </c>
+      <c r="I358" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="359" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="359" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A359" t="s">
         <v>1723</v>
       </c>
@@ -15313,11 +16418,14 @@
       <c r="G359" t="s">
         <v>1037</v>
       </c>
-      <c r="H359" t="s">
+      <c r="H359" s="2">
+        <v>40549</v>
+      </c>
+      <c r="I359" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="360" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="360" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A360" t="s">
         <v>1724</v>
       </c>
@@ -15339,11 +16447,14 @@
       <c r="G360" t="s">
         <v>1040</v>
       </c>
-      <c r="H360" t="s">
+      <c r="H360" s="2">
+        <v>40616</v>
+      </c>
+      <c r="I360" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="361" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="361" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A361" t="s">
         <v>1725</v>
       </c>
@@ -15365,11 +16476,14 @@
       <c r="G361" t="s">
         <v>1043</v>
       </c>
-      <c r="H361" t="s">
+      <c r="H361" s="2">
+        <v>40341</v>
+      </c>
+      <c r="I361" t="s">
         <v>1044</v>
       </c>
     </row>
-    <row r="362" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="362" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A362" t="s">
         <v>1726</v>
       </c>
@@ -15391,11 +16505,14 @@
       <c r="G362" t="s">
         <v>1047</v>
       </c>
-      <c r="H362" t="s">
+      <c r="H362" s="2">
+        <v>40610</v>
+      </c>
+      <c r="I362" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="363" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="363" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A363" t="s">
         <v>1727</v>
       </c>
@@ -15417,11 +16534,14 @@
       <c r="G363" t="s">
         <v>1050</v>
       </c>
-      <c r="H363" t="s">
+      <c r="H363" s="2">
+        <v>40620</v>
+      </c>
+      <c r="I363" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="364" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="364" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A364" t="s">
         <v>1728</v>
       </c>
@@ -15443,11 +16563,14 @@
       <c r="G364" t="s">
         <v>1052</v>
       </c>
-      <c r="H364" t="s">
+      <c r="H364" s="2">
+        <v>40407</v>
+      </c>
+      <c r="I364" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="365" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="365" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A365" t="s">
         <v>1729</v>
       </c>
@@ -15469,11 +16592,14 @@
       <c r="G365" t="s">
         <v>1055</v>
       </c>
-      <c r="H365" t="s">
+      <c r="H365" s="2">
+        <v>40614</v>
+      </c>
+      <c r="I365" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="366" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="366" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A366" t="s">
         <v>1730</v>
       </c>
@@ -15495,11 +16621,14 @@
       <c r="G366" t="s">
         <v>1058</v>
       </c>
-      <c r="H366" t="s">
+      <c r="H366" s="2">
+        <v>40419</v>
+      </c>
+      <c r="I366" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="367" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="367" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A367" t="s">
         <v>1731</v>
       </c>
@@ -15521,11 +16650,14 @@
       <c r="G367" t="s">
         <v>1060</v>
       </c>
-      <c r="H367" t="s">
+      <c r="H367" s="2">
+        <v>40447</v>
+      </c>
+      <c r="I367" t="s">
         <v>466</v>
       </c>
     </row>
-    <row r="368" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="368" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A368" t="s">
         <v>1732</v>
       </c>
@@ -15547,11 +16679,14 @@
       <c r="G368" t="s">
         <v>1062</v>
       </c>
-      <c r="H368" t="s">
+      <c r="H368" s="2">
+        <v>40388</v>
+      </c>
+      <c r="I368" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="369" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="369" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A369" t="s">
         <v>1733</v>
       </c>
@@ -15573,11 +16708,14 @@
       <c r="G369" t="s">
         <v>1064</v>
       </c>
-      <c r="H369" t="s">
+      <c r="H369" s="2">
+        <v>40490</v>
+      </c>
+      <c r="I369" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="370" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="370" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A370" t="s">
         <v>1734</v>
       </c>
@@ -15599,11 +16737,14 @@
       <c r="G370" t="s">
         <v>98</v>
       </c>
-      <c r="H370" t="s">
+      <c r="H370" s="2">
+        <v>40448</v>
+      </c>
+      <c r="I370" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="371" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="371" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A371" t="s">
         <v>1736</v>
       </c>
@@ -15625,11 +16766,14 @@
       <c r="G371" t="s">
         <v>1069</v>
       </c>
-      <c r="H371" t="s">
+      <c r="H371" s="2">
+        <v>40536</v>
+      </c>
+      <c r="I371" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="372" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="372" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A372" t="s">
         <v>1737</v>
       </c>
@@ -15651,11 +16795,14 @@
       <c r="G372" t="s">
         <v>1071</v>
       </c>
-      <c r="H372" t="s">
+      <c r="H372" s="2">
+        <v>40576</v>
+      </c>
+      <c r="I372" t="s">
         <v>1072</v>
       </c>
     </row>
-    <row r="373" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="373" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A373" t="s">
         <v>1738</v>
       </c>
@@ -15677,11 +16824,14 @@
       <c r="G373" t="s">
         <v>422</v>
       </c>
-      <c r="H373" t="s">
+      <c r="H373" s="2">
+        <v>40451</v>
+      </c>
+      <c r="I373" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="374" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="374" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A374" t="s">
         <v>1739</v>
       </c>
@@ -15703,11 +16853,14 @@
       <c r="G374" t="s">
         <v>1077</v>
       </c>
-      <c r="H374" t="s">
+      <c r="H374" s="2">
+        <v>40451</v>
+      </c>
+      <c r="I374" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="375" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="375" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A375" t="s">
         <v>1740</v>
       </c>
@@ -15729,11 +16882,14 @@
       <c r="G375" t="s">
         <v>1080</v>
       </c>
-      <c r="H375" t="s">
+      <c r="H375" s="2">
+        <v>40456</v>
+      </c>
+      <c r="I375" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="376" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="376" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A376" t="s">
         <v>1741</v>
       </c>
@@ -15755,11 +16911,14 @@
       <c r="G376" t="s">
         <v>1082</v>
       </c>
-      <c r="H376" t="s">
+      <c r="H376" s="2">
+        <v>40422</v>
+      </c>
+      <c r="I376" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="377" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="377" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A377" t="s">
         <v>1742</v>
       </c>
@@ -15781,11 +16940,14 @@
       <c r="G377" t="s">
         <v>402</v>
       </c>
-      <c r="H377" t="s">
+      <c r="H377" s="2">
+        <v>40595</v>
+      </c>
+      <c r="I377" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="378" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="378" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A378" t="s">
         <v>1743</v>
       </c>
@@ -15807,11 +16969,14 @@
       <c r="G378" t="s">
         <v>1084</v>
       </c>
-      <c r="H378" t="s">
+      <c r="H378" s="2">
+        <v>40633</v>
+      </c>
+      <c r="I378" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="379" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="379" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A379" t="s">
         <v>1744</v>
       </c>
@@ -15833,11 +16998,14 @@
       <c r="G379" t="s">
         <v>1087</v>
       </c>
-      <c r="H379" t="s">
+      <c r="H379" s="2">
+        <v>40572</v>
+      </c>
+      <c r="I379" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="380" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="380" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A380" t="s">
         <v>1745</v>
       </c>
@@ -15859,11 +17027,14 @@
       <c r="G380" t="s">
         <v>1089</v>
       </c>
-      <c r="H380" t="s">
+      <c r="H380" s="2">
+        <v>40520</v>
+      </c>
+      <c r="I380" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="381" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="381" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A381" t="s">
         <v>1746</v>
       </c>
@@ -15885,11 +17056,14 @@
       <c r="G381" t="s">
         <v>1091</v>
       </c>
-      <c r="H381" t="s">
+      <c r="H381" s="2">
+        <v>40370</v>
+      </c>
+      <c r="I381" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="382" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="382" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A382" t="s">
         <v>1747</v>
       </c>
@@ -15911,11 +17085,14 @@
       <c r="G382" t="s">
         <v>1094</v>
       </c>
-      <c r="H382" t="s">
+      <c r="H382" s="2">
+        <v>40546</v>
+      </c>
+      <c r="I382" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="383" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="383" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A383" t="s">
         <v>1748</v>
       </c>
@@ -15937,11 +17114,14 @@
       <c r="G383" t="s">
         <v>1096</v>
       </c>
-      <c r="H383" t="s">
+      <c r="H383" s="2">
+        <v>40590</v>
+      </c>
+      <c r="I383" t="s">
         <v>480</v>
       </c>
     </row>
-    <row r="384" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="384" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A384" t="s">
         <v>1749</v>
       </c>
@@ -15963,11 +17143,14 @@
       <c r="G384" t="s">
         <v>1099</v>
       </c>
-      <c r="H384" t="s">
+      <c r="H384" s="2">
+        <v>40365</v>
+      </c>
+      <c r="I384" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="385" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="385" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A385" t="s">
         <v>1750</v>
       </c>
@@ -15989,11 +17172,14 @@
       <c r="G385" t="s">
         <v>473</v>
       </c>
-      <c r="H385" t="s">
+      <c r="H385" s="2">
+        <v>40483</v>
+      </c>
+      <c r="I385" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="386" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="386" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A386" t="s">
         <v>1751</v>
       </c>
@@ -16015,11 +17201,14 @@
       <c r="G386" t="s">
         <v>1103</v>
       </c>
-      <c r="H386" t="s">
+      <c r="H386" s="2">
+        <v>40494</v>
+      </c>
+      <c r="I386" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="387" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="387" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A387" t="s">
         <v>1752</v>
       </c>
@@ -16041,11 +17230,14 @@
       <c r="G387" t="s">
         <v>289</v>
       </c>
-      <c r="H387" t="s">
+      <c r="H387" s="2">
+        <v>40624</v>
+      </c>
+      <c r="I387" t="s">
         <v>413</v>
       </c>
     </row>
-    <row r="388" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="388" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A388" t="s">
         <v>1753</v>
       </c>
@@ -16067,11 +17259,14 @@
       <c r="G388" t="s">
         <v>1106</v>
       </c>
-      <c r="H388" t="s">
+      <c r="H388" s="2">
+        <v>40312</v>
+      </c>
+      <c r="I388" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="389" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="389" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A389" t="s">
         <v>1754</v>
       </c>
@@ -16093,11 +17288,14 @@
       <c r="G389" t="s">
         <v>428</v>
       </c>
-      <c r="H389" t="s">
+      <c r="H389" s="2">
+        <v>40567</v>
+      </c>
+      <c r="I389" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="390" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="390" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A390" t="s">
         <v>1755</v>
       </c>
@@ -16119,11 +17317,14 @@
       <c r="G390" t="s">
         <v>1111</v>
       </c>
-      <c r="H390" t="s">
+      <c r="H390" s="2">
+        <v>40489</v>
+      </c>
+      <c r="I390" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="391" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="391" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A391" t="s">
         <v>1756</v>
       </c>
@@ -16145,11 +17346,14 @@
       <c r="G391" t="s">
         <v>428</v>
       </c>
-      <c r="H391" t="s">
+      <c r="H391" s="2">
+        <v>40508</v>
+      </c>
+      <c r="I391" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="392" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="392" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A392" t="s">
         <v>1757</v>
       </c>
@@ -16171,11 +17375,14 @@
       <c r="G392" t="s">
         <v>1116</v>
       </c>
-      <c r="H392" t="s">
+      <c r="H392" s="2">
+        <v>40338</v>
+      </c>
+      <c r="I392" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="393" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="393" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A393" t="s">
         <v>1758</v>
       </c>
@@ -16197,11 +17404,14 @@
       <c r="G393" t="s">
         <v>1119</v>
       </c>
-      <c r="H393" t="s">
+      <c r="H393" s="2">
+        <v>40313</v>
+      </c>
+      <c r="I393" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="394" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="394" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A394" t="s">
         <v>1759</v>
       </c>
@@ -16223,11 +17433,14 @@
       <c r="G394" t="s">
         <v>1121</v>
       </c>
-      <c r="H394" t="s">
+      <c r="H394" s="2">
+        <v>40426</v>
+      </c>
+      <c r="I394" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="395" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="395" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A395" t="s">
         <v>1760</v>
       </c>
@@ -16249,11 +17462,14 @@
       <c r="G395" t="s">
         <v>1124</v>
       </c>
-      <c r="H395" t="s">
+      <c r="H395" s="2">
+        <v>40455</v>
+      </c>
+      <c r="I395" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="396" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="396" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A396" t="s">
         <v>1761</v>
       </c>
@@ -16275,11 +17491,14 @@
       <c r="G396" t="s">
         <v>1126</v>
       </c>
-      <c r="H396" t="s">
+      <c r="H396" s="2">
+        <v>40448</v>
+      </c>
+      <c r="I396" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="397" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="397" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A397" t="s">
         <v>1762</v>
       </c>
@@ -16301,11 +17520,14 @@
       <c r="G397" t="s">
         <v>1128</v>
       </c>
-      <c r="H397" t="s">
+      <c r="H397" s="2">
+        <v>40395</v>
+      </c>
+      <c r="I397" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="398" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="398" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A398" t="s">
         <v>1763</v>
       </c>
@@ -16327,11 +17549,14 @@
       <c r="G398" t="s">
         <v>1131</v>
       </c>
-      <c r="H398" t="s">
+      <c r="H398" s="2">
+        <v>40593</v>
+      </c>
+      <c r="I398" t="s">
         <v>504</v>
       </c>
     </row>
-    <row r="399" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="399" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A399" t="s">
         <v>1764</v>
       </c>
@@ -16353,11 +17578,14 @@
       <c r="G399" t="s">
         <v>1133</v>
       </c>
-      <c r="H399" t="s">
+      <c r="H399" s="2">
+        <v>40372</v>
+      </c>
+      <c r="I399" t="s">
         <v>1134</v>
       </c>
     </row>
-    <row r="400" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="400" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A400" t="s">
         <v>1765</v>
       </c>
@@ -16379,11 +17607,14 @@
       <c r="G400" t="s">
         <v>1137</v>
       </c>
-      <c r="H400" t="s">
+      <c r="H400" s="2">
+        <v>40531</v>
+      </c>
+      <c r="I400" t="s">
         <v>545</v>
       </c>
     </row>
-    <row r="401" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="401" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A401" t="s">
         <v>1766</v>
       </c>
@@ -16405,11 +17636,14 @@
       <c r="G401" t="s">
         <v>1139</v>
       </c>
-      <c r="H401" t="s">
+      <c r="H401" s="2">
+        <v>40603</v>
+      </c>
+      <c r="I401" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="402" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="402" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A402" t="s">
         <v>1767</v>
       </c>
@@ -16431,11 +17665,14 @@
       <c r="G402" t="s">
         <v>1141</v>
       </c>
-      <c r="H402" t="s">
+      <c r="H402" s="2">
+        <v>40431</v>
+      </c>
+      <c r="I402" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="403" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="403" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A403" t="s">
         <v>1768</v>
       </c>
@@ -16457,11 +17694,14 @@
       <c r="G403" t="s">
         <v>1143</v>
       </c>
-      <c r="H403" t="s">
+      <c r="H403" s="2">
+        <v>40309</v>
+      </c>
+      <c r="I403" t="s">
         <v>466</v>
       </c>
     </row>
-    <row r="404" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="404" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A404" t="s">
         <v>1769</v>
       </c>
@@ -16483,11 +17723,14 @@
       <c r="G404" t="s">
         <v>1144</v>
       </c>
-      <c r="H404" t="s">
+      <c r="H404" s="2">
+        <v>40594</v>
+      </c>
+      <c r="I404" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="405" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="405" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A405" t="s">
         <v>1770</v>
       </c>
@@ -16509,11 +17752,14 @@
       <c r="G405" t="s">
         <v>974</v>
       </c>
-      <c r="H405" t="s">
+      <c r="H405" s="2">
+        <v>40312</v>
+      </c>
+      <c r="I405" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="406" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="406" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A406" t="s">
         <v>1771</v>
       </c>
@@ -16535,11 +17781,14 @@
       <c r="G406" t="s">
         <v>823</v>
       </c>
-      <c r="H406" t="s">
+      <c r="H406" s="2">
+        <v>40603</v>
+      </c>
+      <c r="I406" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="407" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="407" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A407" t="s">
         <v>1772</v>
       </c>
@@ -16561,11 +17810,14 @@
       <c r="G407" t="s">
         <v>1148</v>
       </c>
-      <c r="H407" t="s">
+      <c r="H407" s="2">
+        <v>40577</v>
+      </c>
+      <c r="I407" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="408" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="408" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A408" t="s">
         <v>1774</v>
       </c>
@@ -16587,11 +17839,14 @@
       <c r="G408" t="s">
         <v>1150</v>
       </c>
-      <c r="H408" t="s">
+      <c r="H408" s="2">
+        <v>40576</v>
+      </c>
+      <c r="I408" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="409" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="409" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A409" t="s">
         <v>1775</v>
       </c>
@@ -16613,11 +17868,14 @@
       <c r="G409" t="s">
         <v>1153</v>
       </c>
-      <c r="H409" t="s">
+      <c r="H409" s="2">
+        <v>40397</v>
+      </c>
+      <c r="I409" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="410" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="410" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A410" t="s">
         <v>1776</v>
       </c>
@@ -16639,11 +17897,14 @@
       <c r="G410" t="s">
         <v>1157</v>
       </c>
-      <c r="H410" t="s">
+      <c r="H410" s="2">
+        <v>40350</v>
+      </c>
+      <c r="I410" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="411" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="411" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A411" t="s">
         <v>1777</v>
       </c>
@@ -16665,11 +17926,14 @@
       <c r="G411" t="s">
         <v>1160</v>
       </c>
-      <c r="H411" t="s">
+      <c r="H411" s="2">
+        <v>40377</v>
+      </c>
+      <c r="I411" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="412" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="412" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A412" t="s">
         <v>1778</v>
       </c>
@@ -16691,11 +17955,14 @@
       <c r="G412" t="s">
         <v>458</v>
       </c>
-      <c r="H412" t="s">
+      <c r="H412" s="2">
+        <v>40345</v>
+      </c>
+      <c r="I412" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="413" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="413" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A413" t="s">
         <v>1779</v>
       </c>
@@ -16717,11 +17984,14 @@
       <c r="G413" t="s">
         <v>1164</v>
       </c>
-      <c r="H413" t="s">
+      <c r="H413" s="2">
+        <v>40437</v>
+      </c>
+      <c r="I413" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="414" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="414" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A414" t="s">
         <v>1780</v>
       </c>
@@ -16743,11 +18013,14 @@
       <c r="G414" t="s">
         <v>1166</v>
       </c>
-      <c r="H414" t="s">
+      <c r="H414" s="2">
+        <v>40279</v>
+      </c>
+      <c r="I414" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="415" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="415" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A415" t="s">
         <v>1781</v>
       </c>
@@ -16769,11 +18042,14 @@
       <c r="G415" t="s">
         <v>1168</v>
       </c>
-      <c r="H415" t="s">
+      <c r="H415" s="2">
+        <v>40308</v>
+      </c>
+      <c r="I415" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="416" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="416" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A416" t="s">
         <v>1782</v>
       </c>
@@ -16795,11 +18071,14 @@
       <c r="G416" t="s">
         <v>1171</v>
       </c>
-      <c r="H416" t="s">
+      <c r="H416" s="2">
+        <v>40409</v>
+      </c>
+      <c r="I416" t="s">
         <v>628</v>
       </c>
     </row>
-    <row r="417" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="417" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A417" t="s">
         <v>1783</v>
       </c>
@@ -16821,11 +18100,14 @@
       <c r="G417" t="s">
         <v>1174</v>
       </c>
-      <c r="H417" t="s">
+      <c r="H417" s="2">
+        <v>40378</v>
+      </c>
+      <c r="I417" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="418" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="418" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A418" t="s">
         <v>1784</v>
       </c>
@@ -16847,11 +18129,14 @@
       <c r="G418" t="s">
         <v>1176</v>
       </c>
-      <c r="H418" t="s">
+      <c r="H418" s="2">
+        <v>40345</v>
+      </c>
+      <c r="I418" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="419" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="419" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A419" t="s">
         <v>1785</v>
       </c>
@@ -16873,11 +18158,14 @@
       <c r="G419" t="s">
         <v>669</v>
       </c>
-      <c r="H419" t="s">
+      <c r="H419" s="2">
+        <v>40536</v>
+      </c>
+      <c r="I419" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="420" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="420" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A420" t="s">
         <v>1786</v>
       </c>
@@ -16899,11 +18187,14 @@
       <c r="G420" t="s">
         <v>1178</v>
       </c>
-      <c r="H420" t="s">
+      <c r="H420" s="2">
+        <v>40325</v>
+      </c>
+      <c r="I420" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="421" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="421" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A421" t="s">
         <v>1787</v>
       </c>
@@ -16925,11 +18216,14 @@
       <c r="G421" t="s">
         <v>1180</v>
       </c>
-      <c r="H421" t="s">
+      <c r="H421" s="2">
+        <v>40616</v>
+      </c>
+      <c r="I421" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="422" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="422" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A422" t="s">
         <v>1788</v>
       </c>
@@ -16951,11 +18245,14 @@
       <c r="G422" t="s">
         <v>1183</v>
       </c>
-      <c r="H422" t="s">
+      <c r="H422" s="2">
+        <v>40601</v>
+      </c>
+      <c r="I422" t="s">
         <v>453</v>
       </c>
     </row>
-    <row r="423" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="423" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A423" t="s">
         <v>1789</v>
       </c>
@@ -16977,11 +18274,14 @@
       <c r="G423" t="s">
         <v>621</v>
       </c>
-      <c r="H423" t="s">
+      <c r="H423" s="2">
+        <v>40380</v>
+      </c>
+      <c r="I423" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="424" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="424" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A424" t="s">
         <v>1790</v>
       </c>
@@ -17003,11 +18303,14 @@
       <c r="G424" t="s">
         <v>10</v>
       </c>
-      <c r="H424" t="s">
+      <c r="H424" s="2">
+        <v>40539</v>
+      </c>
+      <c r="I424" t="s">
         <v>480</v>
       </c>
     </row>
-    <row r="425" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="425" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A425" t="s">
         <v>1791</v>
       </c>
@@ -17029,11 +18332,14 @@
       <c r="G425" t="s">
         <v>1189</v>
       </c>
-      <c r="H425" t="s">
+      <c r="H425" s="2">
+        <v>40548</v>
+      </c>
+      <c r="I425" t="s">
         <v>557</v>
       </c>
     </row>
-    <row r="426" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="426" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A426" t="s">
         <v>1792</v>
       </c>
@@ -17055,11 +18361,14 @@
       <c r="G426" t="s">
         <v>314</v>
       </c>
-      <c r="H426" t="s">
+      <c r="H426" s="2">
+        <v>40623</v>
+      </c>
+      <c r="I426" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="427" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="427" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A427" t="s">
         <v>1793</v>
       </c>
@@ -17081,11 +18390,14 @@
       <c r="G427" t="s">
         <v>1193</v>
       </c>
-      <c r="H427" t="s">
+      <c r="H427" s="2">
+        <v>40362</v>
+      </c>
+      <c r="I427" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="428" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="428" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A428" t="s">
         <v>1794</v>
       </c>
@@ -17107,11 +18419,14 @@
       <c r="G428" t="s">
         <v>1195</v>
       </c>
-      <c r="H428" t="s">
+      <c r="H428" s="2">
+        <v>40425</v>
+      </c>
+      <c r="I428" t="s">
         <v>545</v>
       </c>
     </row>
-    <row r="429" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="429" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A429" t="s">
         <v>1795</v>
       </c>
@@ -17133,11 +18448,14 @@
       <c r="G429" t="s">
         <v>1198</v>
       </c>
-      <c r="H429" t="s">
+      <c r="H429" s="2">
+        <v>40429</v>
+      </c>
+      <c r="I429" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="430" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="430" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A430" t="s">
         <v>1796</v>
       </c>
@@ -17159,11 +18477,14 @@
       <c r="G430" t="s">
         <v>1201</v>
       </c>
-      <c r="H430" t="s">
+      <c r="H430" s="2">
+        <v>40427</v>
+      </c>
+      <c r="I430" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="431" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="431" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A431" t="s">
         <v>1797</v>
       </c>
@@ -17185,11 +18506,14 @@
       <c r="G431" t="s">
         <v>1204</v>
       </c>
-      <c r="H431" t="s">
+      <c r="H431" s="2">
+        <v>40469</v>
+      </c>
+      <c r="I431" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="432" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="432" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A432" t="s">
         <v>1798</v>
       </c>
@@ -17211,11 +18535,14 @@
       <c r="G432" t="s">
         <v>1206</v>
       </c>
-      <c r="H432" t="s">
+      <c r="H432" s="2">
+        <v>40471</v>
+      </c>
+      <c r="I432" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="433" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="433" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A433" t="s">
         <v>1799</v>
       </c>
@@ -17237,11 +18564,14 @@
       <c r="G433" t="s">
         <v>1209</v>
       </c>
-      <c r="H433" t="s">
+      <c r="H433" s="2">
+        <v>40544</v>
+      </c>
+      <c r="I433" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="434" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="434" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A434" t="s">
         <v>1800</v>
       </c>
@@ -17263,11 +18593,14 @@
       <c r="G434" t="s">
         <v>1212</v>
       </c>
-      <c r="H434" t="s">
+      <c r="H434" s="2">
+        <v>40458</v>
+      </c>
+      <c r="I434" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="435" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="435" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A435" t="s">
         <v>1801</v>
       </c>
@@ -17289,11 +18622,14 @@
       <c r="G435" t="s">
         <v>279</v>
       </c>
-      <c r="H435" t="s">
+      <c r="H435" s="2">
+        <v>40491</v>
+      </c>
+      <c r="I435" t="s">
         <v>1215</v>
       </c>
     </row>
-    <row r="436" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="436" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A436" t="s">
         <v>1802</v>
       </c>
@@ -17315,11 +18651,14 @@
       <c r="G436" t="s">
         <v>541</v>
       </c>
-      <c r="H436" t="s">
+      <c r="H436" s="2">
+        <v>40295</v>
+      </c>
+      <c r="I436" t="s">
         <v>413</v>
       </c>
     </row>
-    <row r="437" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="437" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A437" t="s">
         <v>1803</v>
       </c>
@@ -17341,11 +18680,14 @@
       <c r="G437" t="s">
         <v>1219</v>
       </c>
-      <c r="H437" t="s">
+      <c r="H437" s="2">
+        <v>40274</v>
+      </c>
+      <c r="I437" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="438" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="438" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A438" t="s">
         <v>1804</v>
       </c>
@@ -17367,11 +18709,14 @@
       <c r="G438" t="s">
         <v>1221</v>
       </c>
-      <c r="H438" t="s">
+      <c r="H438" s="2">
+        <v>40608</v>
+      </c>
+      <c r="I438" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="439" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="439" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A439" t="s">
         <v>1805</v>
       </c>
@@ -17393,11 +18738,14 @@
       <c r="G439" t="s">
         <v>1224</v>
       </c>
-      <c r="H439" t="s">
+      <c r="H439" s="2">
+        <v>40290</v>
+      </c>
+      <c r="I439" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="440" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="440" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A440" t="s">
         <v>1806</v>
       </c>
@@ -17419,11 +18767,14 @@
       <c r="G440" t="s">
         <v>1226</v>
       </c>
-      <c r="H440" t="s">
+      <c r="H440" s="2">
+        <v>40276</v>
+      </c>
+      <c r="I440" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="441" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="441" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A441" t="s">
         <v>1807</v>
       </c>
@@ -17445,11 +18796,14 @@
       <c r="G441" t="s">
         <v>1228</v>
       </c>
-      <c r="H441" t="s">
+      <c r="H441" s="2">
+        <v>40353</v>
+      </c>
+      <c r="I441" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="442" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="442" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A442" t="s">
         <v>1808</v>
       </c>
@@ -17471,11 +18825,14 @@
       <c r="G442" t="s">
         <v>1231</v>
       </c>
-      <c r="H442" t="s">
+      <c r="H442" s="2">
+        <v>40449</v>
+      </c>
+      <c r="I442" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="443" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="443" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A443" t="s">
         <v>1809</v>
       </c>
@@ -17497,11 +18854,14 @@
       <c r="G443" t="s">
         <v>1149</v>
       </c>
-      <c r="H443" t="s">
+      <c r="H443" s="2">
+        <v>40500</v>
+      </c>
+      <c r="I443" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="444" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="444" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A444" t="s">
         <v>1810</v>
       </c>
@@ -17523,11 +18883,14 @@
       <c r="G444" t="s">
         <v>1235</v>
       </c>
-      <c r="H444" t="s">
+      <c r="H444" s="2">
+        <v>40587</v>
+      </c>
+      <c r="I444" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="445" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="445" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A445" t="s">
         <v>1812</v>
       </c>
@@ -17549,11 +18912,14 @@
       <c r="G445" t="s">
         <v>1237</v>
       </c>
-      <c r="H445" t="s">
+      <c r="H445" s="2">
+        <v>40620</v>
+      </c>
+      <c r="I445" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="446" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="446" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A446" t="s">
         <v>1813</v>
       </c>
@@ -17575,11 +18941,14 @@
       <c r="G446" t="s">
         <v>1238</v>
       </c>
-      <c r="H446" t="s">
+      <c r="H446" s="2">
+        <v>40322</v>
+      </c>
+      <c r="I446" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="447" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="447" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A447" t="s">
         <v>1814</v>
       </c>
@@ -17601,11 +18970,14 @@
       <c r="G447" t="s">
         <v>1240</v>
       </c>
-      <c r="H447" t="s">
+      <c r="H447" s="2">
+        <v>40396</v>
+      </c>
+      <c r="I447" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="448" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="448" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A448" t="s">
         <v>1815</v>
       </c>
@@ -17627,11 +18999,14 @@
       <c r="G448" t="s">
         <v>1242</v>
       </c>
-      <c r="H448" t="s">
+      <c r="H448" s="2">
+        <v>40402</v>
+      </c>
+      <c r="I448" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="449" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="449" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A449" t="s">
         <v>1816</v>
       </c>
@@ -17653,11 +19028,14 @@
       <c r="G449" t="s">
         <v>1245</v>
       </c>
-      <c r="H449" t="s">
+      <c r="H449" s="2">
+        <v>40567</v>
+      </c>
+      <c r="I449" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="450" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="450" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A450" t="s">
         <v>1817</v>
       </c>
@@ -17679,11 +19057,14 @@
       <c r="G450" t="s">
         <v>1248</v>
       </c>
-      <c r="H450" t="s">
+      <c r="H450" s="2">
+        <v>40274</v>
+      </c>
+      <c r="I450" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="451" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="451" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A451" t="s">
         <v>1818</v>
       </c>
@@ -17705,11 +19086,14 @@
       <c r="G451" t="s">
         <v>1250</v>
       </c>
-      <c r="H451" t="s">
+      <c r="H451" s="2">
+        <v>40434</v>
+      </c>
+      <c r="I451" t="s">
         <v>480</v>
       </c>
     </row>
-    <row r="452" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="452" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A452" t="s">
         <v>1819</v>
       </c>
@@ -17731,11 +19115,14 @@
       <c r="G452" t="s">
         <v>214</v>
       </c>
-      <c r="H452" t="s">
+      <c r="H452" s="2">
+        <v>40359</v>
+      </c>
+      <c r="I452" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="453" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="453" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A453" t="s">
         <v>1820</v>
       </c>
@@ -17757,11 +19144,14 @@
       <c r="G453" t="s">
         <v>1253</v>
       </c>
-      <c r="H453" t="s">
+      <c r="H453" s="2">
+        <v>40627</v>
+      </c>
+      <c r="I453" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="454" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="454" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A454" t="s">
         <v>1821</v>
       </c>
@@ -17783,11 +19173,14 @@
       <c r="G454" t="s">
         <v>1256</v>
       </c>
-      <c r="H454" t="s">
+      <c r="H454" s="2">
+        <v>40365</v>
+      </c>
+      <c r="I454" t="s">
         <v>896</v>
       </c>
     </row>
-    <row r="455" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="455" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A455" t="s">
         <v>1822</v>
       </c>
@@ -17809,11 +19202,14 @@
       <c r="G455" t="s">
         <v>1258</v>
       </c>
-      <c r="H455" t="s">
+      <c r="H455" s="2">
+        <v>40359</v>
+      </c>
+      <c r="I455" t="s">
         <v>855</v>
       </c>
     </row>
-    <row r="456" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="456" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A456" t="s">
         <v>1823</v>
       </c>
@@ -17835,11 +19231,14 @@
       <c r="G456" t="s">
         <v>1259</v>
       </c>
-      <c r="H456" t="s">
+      <c r="H456" s="2">
+        <v>40437</v>
+      </c>
+      <c r="I456" t="s">
         <v>818</v>
       </c>
     </row>
-    <row r="457" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="457" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A457" t="s">
         <v>1824</v>
       </c>
@@ -17861,11 +19260,14 @@
       <c r="G457" t="s">
         <v>1238</v>
       </c>
-      <c r="H457" t="s">
+      <c r="H457" s="2">
+        <v>40406</v>
+      </c>
+      <c r="I457" t="s">
         <v>893</v>
       </c>
     </row>
-    <row r="458" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="458" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A458" t="s">
         <v>1825</v>
       </c>
@@ -17887,11 +19289,14 @@
       <c r="G458" t="s">
         <v>1263</v>
       </c>
-      <c r="H458" t="s">
+      <c r="H458" s="2">
+        <v>40496</v>
+      </c>
+      <c r="I458" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="459" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="459" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A459" t="s">
         <v>1826</v>
       </c>
@@ -17913,11 +19318,14 @@
       <c r="G459" t="s">
         <v>211</v>
       </c>
-      <c r="H459" t="s">
+      <c r="H459" s="2">
+        <v>40461</v>
+      </c>
+      <c r="I459" t="s">
         <v>466</v>
       </c>
     </row>
-    <row r="460" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="460" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A460" t="s">
         <v>1827</v>
       </c>
@@ -17939,11 +19347,14 @@
       <c r="G460" t="s">
         <v>98</v>
       </c>
-      <c r="H460" t="s">
+      <c r="H460" s="2">
+        <v>40595</v>
+      </c>
+      <c r="I460" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="461" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="461" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A461" t="s">
         <v>1828</v>
       </c>
@@ -17965,11 +19376,14 @@
       <c r="G461" t="s">
         <v>1269</v>
       </c>
-      <c r="H461" t="s">
+      <c r="H461" s="2">
+        <v>40606</v>
+      </c>
+      <c r="I461" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="462" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="462" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A462" t="s">
         <v>1829</v>
       </c>
@@ -17991,11 +19405,14 @@
       <c r="G462" t="s">
         <v>1272</v>
       </c>
-      <c r="H462" t="s">
+      <c r="H462" s="2">
+        <v>40386</v>
+      </c>
+      <c r="I462" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="463" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="463" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A463" t="s">
         <v>1830</v>
       </c>
@@ -18017,11 +19434,14 @@
       <c r="G463" t="s">
         <v>1274</v>
       </c>
-      <c r="H463" t="s">
+      <c r="H463" s="2">
+        <v>40421</v>
+      </c>
+      <c r="I463" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="464" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="464" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A464" t="s">
         <v>1831</v>
       </c>
@@ -18043,11 +19463,14 @@
       <c r="G464" t="s">
         <v>197</v>
       </c>
-      <c r="H464" t="s">
+      <c r="H464" s="2">
+        <v>40274</v>
+      </c>
+      <c r="I464" t="s">
         <v>1277</v>
       </c>
     </row>
-    <row r="465" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="465" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A465" t="s">
         <v>1832</v>
       </c>
@@ -18069,11 +19492,14 @@
       <c r="G465" t="s">
         <v>1280</v>
       </c>
-      <c r="H465" t="s">
+      <c r="H465" s="2">
+        <v>40528</v>
+      </c>
+      <c r="I465" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="466" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="466" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A466" t="s">
         <v>1833</v>
       </c>
@@ -18095,11 +19521,14 @@
       <c r="G466" t="s">
         <v>1282</v>
       </c>
-      <c r="H466" t="s">
+      <c r="H466" s="2">
+        <v>40298</v>
+      </c>
+      <c r="I466" t="s">
         <v>466</v>
       </c>
     </row>
-    <row r="467" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="467" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A467" t="s">
         <v>1834</v>
       </c>
@@ -18121,11 +19550,14 @@
       <c r="G467" t="s">
         <v>1285</v>
       </c>
-      <c r="H467" t="s">
+      <c r="H467" s="2">
+        <v>40367</v>
+      </c>
+      <c r="I467" t="s">
         <v>545</v>
       </c>
     </row>
-    <row r="468" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="468" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A468" t="s">
         <v>1835</v>
       </c>
@@ -18147,11 +19579,14 @@
       <c r="G468" t="s">
         <v>1288</v>
       </c>
-      <c r="H468" t="s">
+      <c r="H468" s="2">
+        <v>40590</v>
+      </c>
+      <c r="I468" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="469" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="469" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A469" t="s">
         <v>1836</v>
       </c>
@@ -18173,11 +19608,14 @@
       <c r="G469" t="s">
         <v>1291</v>
       </c>
-      <c r="H469" t="s">
+      <c r="H469" s="2">
+        <v>40387</v>
+      </c>
+      <c r="I469" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="470" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="470" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A470" t="s">
         <v>1837</v>
       </c>
@@ -18199,11 +19637,14 @@
       <c r="G470" t="s">
         <v>317</v>
       </c>
-      <c r="H470" t="s">
+      <c r="H470" s="2">
+        <v>40556</v>
+      </c>
+      <c r="I470" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="471" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="471" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A471" t="s">
         <v>1838</v>
       </c>
@@ -18225,11 +19666,14 @@
       <c r="G471" t="s">
         <v>1294</v>
       </c>
-      <c r="H471" t="s">
+      <c r="H471" s="2">
+        <v>40527</v>
+      </c>
+      <c r="I471" t="s">
         <v>1295</v>
       </c>
     </row>
-    <row r="472" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="472" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A472" t="s">
         <v>1839</v>
       </c>
@@ -18251,11 +19695,14 @@
       <c r="G472" t="s">
         <v>1296</v>
       </c>
-      <c r="H472" t="s">
+      <c r="H472" s="2">
+        <v>40428</v>
+      </c>
+      <c r="I472" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="473" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="473" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A473" t="s">
         <v>1840</v>
       </c>
@@ -18277,11 +19724,14 @@
       <c r="G473" t="s">
         <v>265</v>
       </c>
-      <c r="H473" t="s">
+      <c r="H473" s="2">
+        <v>40400</v>
+      </c>
+      <c r="I473" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="474" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="474" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A474" t="s">
         <v>1841</v>
       </c>
@@ -18303,11 +19753,14 @@
       <c r="G474" t="s">
         <v>1299</v>
       </c>
-      <c r="H474" t="s">
+      <c r="H474" s="2">
+        <v>40579</v>
+      </c>
+      <c r="I474" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="475" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="475" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A475" t="s">
         <v>1842</v>
       </c>
@@ -18329,11 +19782,14 @@
       <c r="G475" t="s">
         <v>1302</v>
       </c>
-      <c r="H475" t="s">
+      <c r="H475" s="2">
+        <v>40417</v>
+      </c>
+      <c r="I475" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="476" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="476" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A476" t="s">
         <v>1843</v>
       </c>
@@ -18355,11 +19811,14 @@
       <c r="G476" t="s">
         <v>2</v>
       </c>
-      <c r="H476" t="s">
+      <c r="H476" s="2">
+        <v>40591</v>
+      </c>
+      <c r="I476" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="477" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="477" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A477" t="s">
         <v>1844</v>
       </c>
@@ -18381,11 +19840,14 @@
       <c r="G477" t="s">
         <v>169</v>
       </c>
-      <c r="H477" t="s">
+      <c r="H477" s="2">
+        <v>40287</v>
+      </c>
+      <c r="I477" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="478" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="478" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A478" t="s">
         <v>1845</v>
       </c>
@@ -18407,11 +19869,14 @@
       <c r="G478" t="s">
         <v>409</v>
       </c>
-      <c r="H478" t="s">
+      <c r="H478" s="2">
+        <v>40451</v>
+      </c>
+      <c r="I478" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="479" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="479" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A479" t="s">
         <v>1846</v>
       </c>
@@ -18433,7 +19898,10 @@
       <c r="G479" t="s">
         <v>1308</v>
       </c>
-      <c r="H479" t="s">
+      <c r="H479" s="2">
+        <v>40534</v>
+      </c>
+      <c r="I479" t="s">
         <v>576</v>
       </c>
     </row>
